--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Peacock_2024_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Peacock_2024_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{EB5A70C5-0542-CC4D-B2C3-B66A3176FC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8978432-6DE3-459E-8395-F72F9F10AC4E}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="1" r:id="rId1"/>
@@ -797,13 +797,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,7 +915,7 @@
         </row>
         <row r="19">
           <cell r="C19">
-            <v>0.8</v>
+            <v>1.7</v>
           </cell>
         </row>
         <row r="21">
@@ -960,12 +960,12 @@
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1282</v>
+            <v>1371</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>480</v>
+            <v>523</v>
           </cell>
         </row>
       </sheetData>
@@ -1523,123 +1523,123 @@
       </c>
       <c r="C3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!C1</f>
-        <v>1198130841.1214952</v>
+        <v>1281308411.2149532</v>
       </c>
       <c r="D3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!D1</f>
-        <v>1119748449.6462574</v>
+        <v>1197484496.4625731</v>
       </c>
       <c r="E3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!E1</f>
-        <v>1046493878.1740721</v>
+        <v>1119144389.2173579</v>
       </c>
       <c r="F3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!F1</f>
-        <v>978031661.84492731</v>
+        <v>1045929335.7171571</v>
       </c>
       <c r="G3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!G1</f>
-        <v>914048282.09806287</v>
+        <v>977504052.07210934</v>
       </c>
       <c r="H3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!H1</f>
-        <v>854250730.93276906</v>
+        <v>913555188.85243869</v>
       </c>
       <c r="I3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!I1</f>
-        <v>798365169.09604585</v>
+        <v>853789896.12377441</v>
       </c>
       <c r="J3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!J1</f>
-        <v>746135672.05237925</v>
+        <v>797934482.35866773</v>
       </c>
       <c r="K3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!K1</f>
-        <v>697323057.99287772</v>
+        <v>745733161.08286691</v>
       </c>
       <c r="L3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!L1</f>
-        <v>651703792.51670825</v>
+        <v>696946879.51669812</v>
       </c>
       <c r="M3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!M1</f>
-        <v>609068964.96888614</v>
+        <v>651352223.84738135</v>
       </c>
       <c r="N3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!N1</f>
-        <v>569223331.74662268</v>
+        <v>608740396.11904812</v>
       </c>
       <c r="O3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!O1</f>
-        <v>531984422.19310522</v>
+        <v>568916258.05518508</v>
       </c>
       <c r="P3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!P1</f>
-        <v>497181702.98421049</v>
+        <v>531697437.43475246</v>
       </c>
       <c r="Q3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!Q1</f>
-        <v>464655797.18150508</v>
+        <v>496913492.9296751</v>
       </c>
       <c r="R3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!R1</f>
-        <v>434257754.37523848</v>
+        <v>464405133.57913566</v>
       </c>
       <c r="S3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!S1</f>
-        <v>405848368.5749892</v>
+        <v>434023489.32629502</v>
       </c>
       <c r="T3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!T1</f>
-        <v>379297540.724289</v>
+        <v>405629429.2769112</v>
       </c>
       <c r="U3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!U1</f>
-        <v>354483682.91989625</v>
+        <v>379092924.55786091</v>
       </c>
       <c r="V3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!V1</f>
-        <v>331293161.60737967</v>
+        <v>354292452.85781401</v>
       </c>
       <c r="W3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!W1</f>
-        <v>309619777.20315856</v>
+        <v>331114441.92319059</v>
       </c>
       <c r="X3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!X1</f>
-        <v>289364277.75996125</v>
+        <v>309452749.46092582</v>
       </c>
       <c r="Y3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!Y1</f>
-        <v>270433904.44856191</v>
+        <v>289208177.06628579</v>
       </c>
       <c r="Z3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!Z1</f>
-        <v>252741966.77435693</v>
+        <v>270288015.94979984</v>
       </c>
       <c r="AA3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AA1</f>
-        <v>236207445.58351114</v>
+        <v>252605622.38299045</v>
       </c>
       <c r="AB3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AB1</f>
-        <v>220754622.04066464</v>
+        <v>236080020.91868269</v>
       </c>
       <c r="AC3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AC1</f>
-        <v>206312730.87912577</v>
+        <v>220635533.56886229</v>
       </c>
       <c r="AD3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AD1</f>
-        <v>192815636.33563161</v>
+        <v>206201433.24192742</v>
       </c>
       <c r="AE3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AE1</f>
-        <v>180201529.28563702</v>
+        <v>192711619.85226861</v>
       </c>
       <c r="AF3">
         <f>('Cost Components'!$B$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AF1</f>
-        <v>168412644.19218412</v>
+        <v>180104317.61894262</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B9" s="16">
         <f>SUM(B3:AF3) / SUM($B$3:$AF$6)</f>
-        <v>0.65402570669691862</v>
+        <v>0.66905215553408037</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B10" s="16">
         <f t="shared" ref="B10:B12" si="0">SUM(B4:AF4) / SUM($B$3:$AF$6)</f>
-        <v>0.20866713455428176</v>
+        <v>0.19960424727603457</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B11" s="16">
         <f t="shared" si="0"/>
-        <v>4.5223196144437823E-2</v>
+        <v>4.3259050090031316E-2</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B12" s="16">
         <f t="shared" si="0"/>
-        <v>9.2083962604363384E-2</v>
+        <v>8.8084547099855262E-2</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -2052,123 +2052,123 @@
       </c>
       <c r="C15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!C1</f>
-        <v>448598130.84112149</v>
+        <v>488785046.72897196</v>
       </c>
       <c r="D15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!D1</f>
-        <v>419250589.5711416</v>
+        <v>456808454.8868897</v>
       </c>
       <c r="E15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!E1</f>
-        <v>391822980.90760893</v>
+        <v>426923789.61391556</v>
       </c>
       <c r="F15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!F1</f>
-        <v>366189701.78281212</v>
+        <v>398994195.90085572</v>
       </c>
       <c r="G15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!G1</f>
-        <v>342233366.15216082</v>
+        <v>372891771.86995852</v>
       </c>
       <c r="H15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!H1</f>
-        <v>319844267.43192601</v>
+        <v>348496983.05603606</v>
       </c>
       <c r="I15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!I1</f>
-        <v>298919876.10460371</v>
+        <v>325698115.00564116</v>
       </c>
       <c r="J15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!J1</f>
-        <v>279364370.19121844</v>
+        <v>304390761.68751508</v>
       </c>
       <c r="K15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!K1</f>
-        <v>261088196.44039103</v>
+        <v>284477347.37150943</v>
       </c>
       <c r="L15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!L1</f>
-        <v>244007660.22466454</v>
+        <v>265866679.78645742</v>
       </c>
       <c r="M15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!M1</f>
-        <v>228044542.26604161</v>
+        <v>248473532.51070783</v>
       </c>
       <c r="N15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!N1</f>
-        <v>213125740.43555292</v>
+        <v>232218254.68290454</v>
       </c>
       <c r="O15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!O1</f>
-        <v>199182934.98649806</v>
+        <v>217026406.24570519</v>
       </c>
       <c r="P15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!P1</f>
-        <v>186152275.68831596</v>
+        <v>202828417.05206093</v>
       </c>
       <c r="Q15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!Q1</f>
-        <v>173974089.42833266</v>
+        <v>189559268.27295411</v>
       </c>
       <c r="R15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!R1</f>
-        <v>162592606.94236699</v>
+        <v>177158194.64762068</v>
       </c>
       <c r="S15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!S1</f>
-        <v>151955707.42277288</v>
+        <v>165568406.2127296</v>
       </c>
       <c r="T15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!T1</f>
-        <v>142014679.83436716</v>
+        <v>154736828.23619589</v>
       </c>
       <c r="U15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!U1</f>
-        <v>132723999.84520295</v>
+        <v>144613858.16466907</v>
       </c>
       <c r="V15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!V1</f>
-        <v>124041121.35065697</v>
+        <v>135153138.47165334</v>
       </c>
       <c r="W15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!W1</f>
-        <v>115926281.63612801</v>
+        <v>126311344.36603114</v>
       </c>
       <c r="X15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!X1</f>
-        <v>108342319.28610094</v>
+        <v>118047985.38881415</v>
       </c>
       <c r="Y15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!Y1</f>
-        <v>101254504.00570181</v>
+        <v>110325219.98954594</v>
       </c>
       <c r="Z15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!Z1</f>
-        <v>94630377.575422257</v>
+        <v>103107682.2332205</v>
       </c>
       <c r="AA15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AA1</f>
-        <v>88439605.210675001</v>
+        <v>96362319.844131306</v>
       </c>
       <c r="AB15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AB1</f>
-        <v>82653836.645490661</v>
+        <v>90058242.844982535</v>
       </c>
       <c r="AC15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AC1</f>
-        <v>77246576.304196864</v>
+        <v>84166582.098114491</v>
       </c>
       <c r="AD15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AD1</f>
-        <v>72193061.96653913</v>
+        <v>78660357.1010416</v>
       </c>
       <c r="AE15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AE1</f>
-        <v>67470151.370597318</v>
+        <v>73514352.430879995</v>
       </c>
       <c r="AF15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AF1</f>
-        <v>63056216.234203108</v>
+        <v>68705002.271850467</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B21" s="16">
         <f>SUM(B15:AF15) / SUM($B$15:$AF$18)</f>
-        <v>0.48595529474949106</v>
+        <v>0.50739989886540982</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.25">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B22" s="16">
         <f t="shared" ref="B22:B24" si="1">SUM(B16:AF16) / SUM($B$15:$AF$18)</f>
-        <v>0.30194704356287316</v>
+        <v>0.28935060059392492</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="B23" s="16">
         <f t="shared" si="1"/>
-        <v>6.9348293854972792E-2</v>
+        <v>6.6455263944063481E-2</v>
       </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.25">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B24" s="16">
         <f t="shared" si="1"/>
-        <v>0.14274936783266295</v>
+        <v>0.13679423659660192</v>
       </c>
     </row>
   </sheetData>
@@ -2598,30 +2598,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="H1" s="28" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="H1" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="O1" s="28" t="s">
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="O1" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -2696,11 +2696,11 @@
       </c>
       <c r="E3" s="14">
         <f>'LCOF CO2 Cost Corrected'!B10</f>
-        <v>11.140505415570722</v>
+        <v>11.705907867765633</v>
       </c>
       <c r="F3" s="14">
         <f>'LCOF WACC Corrected '!B10</f>
-        <v>11.084702911966531</v>
+        <v>11.650105364161435</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>172</v>
@@ -2718,11 +2718,11 @@
       </c>
       <c r="L3" s="14">
         <f>'LCOF CO2 Cost Corrected'!B21</f>
-        <v>11.428679860916159</v>
+        <v>11.994082313111065</v>
       </c>
       <c r="M3" s="14">
         <f>'LCOF WACC Corrected '!B21</f>
-        <v>11.37287735731196</v>
+        <v>11.938279809506865</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>172</v>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="S3" s="14">
         <f>'LCOF CO2 Cost Corrected'!B32</f>
-        <v>11.255461144747709</v>
+        <v>11.820863596942624</v>
       </c>
       <c r="T3" s="14">
         <f>'LCOF WACC Corrected '!B32</f>
-        <v>11.19019722051457</v>
+        <v>11.755599672709472</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2764,11 +2764,11 @@
       </c>
       <c r="E4" s="14">
         <f>E3/Inputs!$C$6</f>
-        <v>12.378339350634135</v>
+        <v>13.00656429751737</v>
       </c>
       <c r="F4" s="14">
         <f>F3/Inputs!$C$6</f>
-        <v>12.3163365688517</v>
+        <v>12.944561515734927</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>172</v>
@@ -2786,11 +2786,11 @@
       </c>
       <c r="L4" s="14">
         <f>L3/Inputs!$C$6</f>
-        <v>12.698533178795731</v>
+        <v>13.32675812567896</v>
       </c>
       <c r="M4" s="14">
         <f>M3/Inputs!$C$6</f>
-        <v>12.636530397013289</v>
+        <v>13.264755343896516</v>
       </c>
       <c r="O4" s="11" t="s">
         <v>172</v>
@@ -2808,11 +2808,11 @@
       </c>
       <c r="S4" s="14">
         <f>S3/Inputs!$C$6</f>
-        <v>12.506067938608565</v>
+        <v>13.134292885491805</v>
       </c>
       <c r="T4" s="14">
         <f>T3/Inputs!$C$6</f>
-        <v>12.43355246723841</v>
+        <v>13.061777414121636</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -3172,11 +3172,11 @@
       </c>
       <c r="E10" s="14">
         <f>(E4-E5) / E9 * 10^6</f>
-        <v>4046.1354167126142</v>
+        <v>4265.6732217699036</v>
       </c>
       <c r="F10" s="14">
         <f>(F4-F5) / F9 * 10^6</f>
-        <v>4024.4680908805312</v>
+        <v>4244.0058959378184</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>180</v>
@@ -3194,11 +3194,11 @@
       </c>
       <c r="L10" s="14">
         <f>(L4-L5) / L9 * 10^6</f>
-        <v>4158.029493151691</v>
+        <v>4377.5672982089782</v>
       </c>
       <c r="M10" s="14">
         <f>(M4-M5) / M9 * 10^6</f>
-        <v>4136.3621673196058</v>
+        <v>4355.899972376892</v>
       </c>
       <c r="O10" s="11" t="s">
         <v>180</v>
@@ -3216,38 +3216,38 @@
       </c>
       <c r="S10" s="14">
         <f>(S4-S5) / S9 * 10^6</f>
-        <v>4090.7711065019043</v>
+        <v>4310.3089115591947</v>
       </c>
       <c r="T10" s="14">
         <f>(T4-T5) / T9 * 10^6</f>
-        <v>4065.430044361216</v>
+        <v>4284.9678494185027</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="H13" s="28" t="s">
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="H13" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="O13" s="28" t="s">
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="O13" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
@@ -3322,11 +3322,11 @@
       </c>
       <c r="E15" s="14">
         <f>'LCOF CO2 Cost Corrected'!B43</f>
-        <v>5.4046364232797934</v>
+        <v>5.677808394564976</v>
       </c>
       <c r="F15" s="14">
         <f>'LCOF WACC Corrected '!B43</f>
-        <v>5.3611815056150789</v>
+        <v>5.634353476900257</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>172</v>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="L15" s="14">
         <f>'LCOF CO2 Cost Corrected'!B54</f>
-        <v>5.2420466058736945</v>
+        <v>5.5152185771588691</v>
       </c>
       <c r="M15" s="14">
         <f>'LCOF WACC Corrected '!B54</f>
-        <v>5.1985916882089755</v>
+        <v>5.4717636594941528</v>
       </c>
       <c r="O15" s="11" t="s">
         <v>172</v>
@@ -3366,11 +3366,11 @@
       </c>
       <c r="S15" s="14">
         <f>'LCOF CO2 Cost Corrected'!B65</f>
-        <v>4.9058927958421643</v>
+        <v>5.179064767127346</v>
       </c>
       <c r="T15" s="14">
         <f>'LCOF WACC Corrected '!B65</f>
-        <v>4.8649780783648957</v>
+        <v>5.1381500496500747</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3390,11 +3390,11 @@
       </c>
       <c r="E16" s="14">
         <f>E15/Inputs!$C$6</f>
-        <v>6.0051515814219929</v>
+        <v>6.3086759939610841</v>
       </c>
       <c r="F16" s="14">
         <f>F15/Inputs!$C$6</f>
-        <v>5.9568683395723099</v>
+        <v>6.2603927521113967</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>172</v>
@@ -3412,11 +3412,11 @@
       </c>
       <c r="L16" s="14">
         <f>L15/Inputs!$C$6</f>
-        <v>5.8244962287485498</v>
+        <v>6.1280206412876321</v>
       </c>
       <c r="M16" s="14">
         <f>M15/Inputs!$C$6</f>
-        <v>5.7762129868988614</v>
+        <v>6.0797373994379473</v>
       </c>
       <c r="O16" s="11" t="s">
         <v>172</v>
@@ -3434,11 +3434,11 @@
       </c>
       <c r="S16" s="14">
         <f>S15/Inputs!$C$6</f>
-        <v>5.4509919953801829</v>
+        <v>5.7545164079192732</v>
       </c>
       <c r="T16" s="14">
         <f>T15/Inputs!$C$6</f>
-        <v>5.4055311981832173</v>
+        <v>5.7090556107223049</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3450,19 +3450,19 @@
       </c>
       <c r="C17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="E17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="F17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>174</v>
@@ -3472,19 +3472,19 @@
       </c>
       <c r="J17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="K17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="L17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="M17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="O17" s="11" t="s">
         <v>174</v>
@@ -3494,19 +3494,19 @@
       </c>
       <c r="Q17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="R17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="S17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="T17" s="14">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3790,19 +3790,19 @@
       </c>
       <c r="C22" s="14">
         <f>(C16-C17) / C21 * 10^6</f>
-        <v>1120.7136225660461</v>
+        <v>806.20203633913934</v>
       </c>
       <c r="D22" s="14">
         <f>(D16-D17) / D21 * 10^6</f>
-        <v>633.93170739745119</v>
+        <v>319.42012117054469</v>
       </c>
       <c r="E22" s="14">
         <f>(E16-E17) / E21 * 10^6</f>
-        <v>1818.9783115828025</v>
+        <v>1610.5355525184063</v>
       </c>
       <c r="F22" s="14">
         <f>(F16-F17) / F21 * 10^6</f>
-        <v>1802.1053793802234</v>
+        <v>1593.662620315826</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>180</v>
@@ -3812,19 +3812,19 @@
       </c>
       <c r="J22" s="14">
         <f>(J16-J17) / J21 * 10^6</f>
-        <v>952.97687263463717</v>
+        <v>638.46528640773045</v>
       </c>
       <c r="K22" s="14">
         <f>(K16-K17) / K21 * 10^6</f>
-        <v>630.48609335474259</v>
+        <v>315.97450712783603</v>
       </c>
       <c r="L22" s="14">
         <f>(L16-L17) / L21 * 10^6</f>
-        <v>1755.846976549796</v>
+        <v>1547.4042174853969</v>
       </c>
       <c r="M22" s="14">
         <f>(M16-M17) / M21 * 10^6</f>
-        <v>1738.9740443472151</v>
+        <v>1530.5312852828172</v>
       </c>
       <c r="O22" s="11" t="s">
         <v>180</v>
@@ -3834,37 +3834,37 @@
       </c>
       <c r="Q22" s="14">
         <f>(Q16-Q17) / Q21 * 10^6</f>
-        <v>826.99703717294017</v>
+        <v>512.48545094603355</v>
       </c>
       <c r="R22" s="14">
         <f>(R16-R17) / R21 * 10^6</f>
-        <v>555.33360897520333</v>
+        <v>240.8220227482968</v>
       </c>
       <c r="S22" s="14">
         <f>(S16-S17) / S21 * 10^6</f>
-        <v>1625.3231888840742</v>
+        <v>1416.8804298196776</v>
       </c>
       <c r="T22" s="14">
         <f>(T16-T17) / T21 * 10^6</f>
-        <v>1609.4365806201215</v>
+        <v>1400.9938215557243</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="H24" s="30" t="s">
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="H24" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="O24" s="30" t="s">
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="O24" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="30"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="C27" s="19">
         <f>C26*Inputs!$C$32 * 10^-6</f>
-        <v>0.27612706524480007</v>
+        <v>0.29529657289440003</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>188</v>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="J27" s="19">
         <f>J26*Inputs!$C$32 * 10^-6</f>
-        <v>0.27612706524480007</v>
+        <v>0.29529657289440003</v>
       </c>
       <c r="O27" s="18" t="s">
         <v>188</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="Q27" s="19">
         <f>Q26*Inputs!$C$32 * 10^-6</f>
-        <v>0.27612706524480007</v>
+        <v>0.29529657289440003</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="C28" s="19">
         <f>F4+C27</f>
-        <v>12.5924636340965</v>
+        <v>13.239858088629328</v>
       </c>
       <c r="H28" s="18" t="s">
         <v>189</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="J28" s="19">
         <f>M4+J27</f>
-        <v>12.912657462258089</v>
+        <v>13.560051916790917</v>
       </c>
       <c r="O28" s="18" t="s">
         <v>189</v>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Q28" s="19">
         <f>T4+Q27</f>
-        <v>12.709679532483211</v>
+        <v>13.357073987016037</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C29" s="5">
         <f>(C28-C17) /C21 * 10^6</f>
-        <v>4120.9627145364457</v>
+        <v>4032.6878580980092</v>
       </c>
       <c r="H29" s="18" t="s">
         <v>190</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="J29" s="5">
         <f>(J28-J17) /J21 * 10^6</f>
-        <v>4232.8567909755193</v>
+        <v>4144.5819345370837</v>
       </c>
       <c r="O29" s="18" t="s">
         <v>190</v>
@@ -4020,25 +4020,25 @@
       </c>
       <c r="Q29" s="5">
         <f>(Q28-Q17) /Q21 * 10^6</f>
-        <v>4161.92466801713</v>
+        <v>4073.6498115786935</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="H31" s="30" t="s">
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="H31" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="O31" s="30" t="s">
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="O31" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="C34" s="19">
         <f>C33*Inputs!$C$33 * 10^-6</f>
-        <v>0.10338610867200002</v>
+        <v>0.11264778090720001</v>
       </c>
       <c r="H34" s="18" t="s">
         <v>188</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="J34" s="19">
         <f>J33*Inputs!$C$33 * 10^-6</f>
-        <v>0.10338610867200002</v>
+        <v>0.11264778090720001</v>
       </c>
       <c r="O34" s="18" t="s">
         <v>188</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="Q34" s="19">
         <f>Q33*Inputs!$C$33 * 10^-6</f>
-        <v>0.10338610867200002</v>
+        <v>0.11264778090720001</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C35" s="19">
         <f>F16+C34</f>
-        <v>6.0602544482443097</v>
+        <v>6.3730405330185969</v>
       </c>
       <c r="H35" s="18" t="s">
         <v>189</v>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="J35" s="19">
         <f>M16+J34</f>
-        <v>5.8795990955708612</v>
+        <v>6.1923851803451475</v>
       </c>
       <c r="O35" s="18" t="s">
         <v>189</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="Q35" s="19">
         <f>T16+Q34</f>
-        <v>5.5089173068552171</v>
+        <v>5.8217033916295051</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C36" s="5">
         <f>(C35-C17) /C21 * 10^6</f>
-        <v>1838.2344116382878</v>
+        <v>1633.0282117136753</v>
       </c>
       <c r="H36" s="18" t="s">
         <v>190</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="J36" s="5">
         <f>(J35-J17) /J21 * 10^6</f>
-        <v>1775.1030766052795</v>
+        <v>1569.8968766806668</v>
       </c>
       <c r="O36" s="18" t="s">
         <v>190</v>
@@ -4194,23 +4194,23 @@
       </c>
       <c r="Q36" s="5">
         <f>(Q35-Q17) /Q21 * 10^6</f>
-        <v>1645.5656128781859</v>
+        <v>1440.3594129535736</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="O13:T13"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="O24:Q24"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="H31:J31"/>
     <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="O13:T13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="C18" s="5">
         <f>[1]Inputs!C19</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D18" t="s">
         <v>41</v>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="C32" s="5">
         <f>[1]Inputs!C33</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="D32" t="s">
         <v>49</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="C33" s="5">
         <f>[1]Inputs!C34</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="D33" t="s">
         <v>49</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="B24" s="14">
         <f>(Inputs!$C$32*'Study Parameters'!$C$10*10^6) / 10^6</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>134</v>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="H24" s="14">
         <f>(Inputs!$C$32*'Study Parameters'!$C$10*10^6) / 10^6</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>134</v>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="N24" s="14">
         <f>(Inputs!$C$32*'Study Parameters'!$C$10*10^6) / 10^6</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="O24" s="9" t="s">
         <v>134</v>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T24" s="14">
         <f>(Inputs!$C$33*'Study Parameters'!$C$10*10^6) / 10^6</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="U24" s="9" t="s">
         <v>134</v>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="Z24" s="14">
         <f>(Inputs!$C$33*'Study Parameters'!$C$10*10^6) / 10^6</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="AA24" s="9" t="s">
         <v>134</v>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AF24" s="14">
         <f>(Inputs!$C$33*'Study Parameters'!$C$10*10^6) / 10^6</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="AG24" s="9" t="s">
         <v>134</v>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="B26" s="15">
         <f>B16-B12 - B13 - B14+B25+B24</f>
-        <v>1767.2610169491527</v>
+        <v>1856.2610169491527</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>134</v>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="H26" s="15">
         <f>H16-H12 - H13 - H14+H25+H24</f>
-        <v>1812.6225563909775</v>
+        <v>1901.6225563909775</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>134</v>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="N26" s="15">
         <f>N16-N12 - N13 - N14+N25+N24</f>
-        <v>1727.7619047619046</v>
+        <v>1816.7619047619046</v>
       </c>
       <c r="O26" s="12" t="s">
         <v>134</v>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="T26" s="15">
         <f>T16-T12 - T13 - T14+T25+T24</f>
-        <v>893.83999999999992</v>
+        <v>936.83999999999992</v>
       </c>
       <c r="U26" s="12" t="s">
         <v>134</v>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="Z26" s="15">
         <f>Z16-Z12 - Z13 - Z14+Z25+Z24</f>
-        <v>868.24673684210529</v>
+        <v>911.24673684210529</v>
       </c>
       <c r="AA26" s="12" t="s">
         <v>134</v>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="AF26" s="15">
         <f>AF16-AF12 - AF13 - AF14+AF25+AF24</f>
-        <v>819.40463157894737</v>
+        <v>862.40463157894737</v>
       </c>
       <c r="AG26" s="12" t="s">
         <v>134</v>
@@ -8390,6 +8390,24 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="Y2:AC2"/>
+    <mergeCell ref="AE2:AI2"/>
+    <mergeCell ref="M10:Q10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="AE1:AI1"/>
+    <mergeCell ref="Y1:AC1"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="S1:W1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="S18:W18"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="S2:W2"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="S10:W10"/>
+    <mergeCell ref="G2:K2"/>
     <mergeCell ref="AE19:AI19"/>
     <mergeCell ref="AE10:AI10"/>
     <mergeCell ref="M18:Q18"/>
@@ -8402,24 +8420,6 @@
     <mergeCell ref="Y19:AC19"/>
     <mergeCell ref="Y10:AC10"/>
     <mergeCell ref="S19:W19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="S18:W18"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="S2:W2"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="S10:W10"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="Y2:AC2"/>
-    <mergeCell ref="AE2:AI2"/>
-    <mergeCell ref="M10:Q10"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="AE1:AI1"/>
-    <mergeCell ref="Y1:AC1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="S1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19168,123 +19168,123 @@
       </c>
       <c r="C3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="D3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="E3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="F3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="G3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="H3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="I3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="J3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="K3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="L3">
         <f>'Cost Components'!$B$26 * 10^6 + 'Cost Components'!$B$7*10^6</f>
-        <v>1944261016.9491527</v>
+        <v>2033261016.9491527</v>
       </c>
       <c r="M3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="N3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="O3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="P3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="Q3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="R3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="S3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="T3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="U3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="V3">
         <f>'Cost Components'!$B$26 * 10^6 + 'Cost Components'!$B$7*10^6</f>
-        <v>1944261016.9491527</v>
+        <v>2033261016.9491527</v>
       </c>
       <c r="W3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="X3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="Y3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="Z3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AA3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AB3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AC3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AD3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AE3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AF3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -19297,123 +19297,123 @@
       </c>
       <c r="C4">
         <f>C3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!C2</f>
-        <v>1636352793.4714377</v>
+        <v>1718760200.878845</v>
       </c>
       <c r="D4">
         <f>D3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!D2</f>
-        <v>1515141475.4365163</v>
+        <v>1591444630.4433749</v>
       </c>
       <c r="E4">
         <f>E3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!E2</f>
-        <v>1402908773.5523298</v>
+        <v>1473559843.003125</v>
       </c>
       <c r="F4">
         <f>F3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!F2</f>
-        <v>1298989605.141046</v>
+        <v>1364407262.0399303</v>
       </c>
       <c r="G4">
         <f>G3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!G2</f>
-        <v>1202768152.908376</v>
+        <v>1263340057.44438</v>
       </c>
       <c r="H4">
         <f>H3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!H2</f>
-        <v>1113674215.6559036</v>
+        <v>1169759312.4484997</v>
       </c>
       <c r="I4">
         <f>I3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!I2</f>
-        <v>1031179829.3110217</v>
+        <v>1083110474.4893515</v>
       </c>
       <c r="J4">
         <f>J3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!J2</f>
-        <v>954796138.25094604</v>
+        <v>1002880068.9716219</v>
       </c>
       <c r="K4">
         <f>K3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!K2</f>
-        <v>884070498.38050556</v>
+        <v>928592656.45520532</v>
       </c>
       <c r="L4">
         <f>L3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!L2</f>
-        <v>900569042.18775344</v>
+        <v>941793262.62729037</v>
       </c>
       <c r="M4">
         <f>M3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!M2</f>
-        <v>757947958.14515221</v>
+        <v>796118532.62620485</v>
       </c>
       <c r="N4">
         <f>N3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!N2</f>
-        <v>701803664.94921494</v>
+        <v>737146789.46870816</v>
       </c>
       <c r="O4">
         <f>O3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!O2</f>
-        <v>649818208.28631008</v>
+        <v>682543323.58213723</v>
       </c>
       <c r="P4">
         <f>P3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!P2</f>
-        <v>601683526.19102776</v>
+        <v>631984558.87234914</v>
       </c>
       <c r="Q4">
         <f>Q3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!Q2</f>
-        <v>557114376.10280347</v>
+        <v>585170887.84476769</v>
       </c>
       <c r="R4">
         <f>R3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!R2</f>
-        <v>515846644.53963286</v>
+        <v>541824896.15256262</v>
       </c>
       <c r="S4">
         <f>S3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!S2</f>
-        <v>477635781.98114151</v>
+        <v>501689718.6597802</v>
       </c>
       <c r="T4">
         <f>T3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!T2</f>
-        <v>442255353.6862421</v>
+        <v>464527517.27757424</v>
       </c>
       <c r="U4">
         <f>U3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!U2</f>
-        <v>409495697.8576315</v>
+        <v>430118071.55330944</v>
       </c>
       <c r="V4">
         <f>V3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!V2</f>
-        <v>417137715.91202873</v>
+        <v>436232506.37098974</v>
       </c>
       <c r="W4">
         <f>W3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!W2</f>
-        <v>351076558.51991731</v>
+        <v>368756920.05599231</v>
       </c>
       <c r="X4">
         <f>X3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!X2</f>
-        <v>325070887.51844192</v>
+        <v>341441592.64443731</v>
       </c>
       <c r="Y4">
         <f>Y3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!Y2</f>
-        <v>300991562.51707584</v>
+        <v>316149622.81892341</v>
       </c>
       <c r="Z4">
         <f>Z3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!Z2</f>
-        <v>278695891.21951467</v>
+        <v>292731132.23974389</v>
       </c>
       <c r="AA4">
         <f>AA3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!AA2</f>
-        <v>258051751.12918019</v>
+        <v>271047344.66642952</v>
       </c>
       <c r="AB4">
         <f>AB3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!AB2</f>
-        <v>238936806.60109279</v>
+        <v>250969763.58002734</v>
       </c>
       <c r="AC4">
         <f>AC3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!AC2</f>
-        <v>221237783.88990071</v>
+        <v>232379410.72224751</v>
       </c>
       <c r="AD4">
         <f>AD3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!AD2</f>
-        <v>204849799.89805624</v>
+        <v>215166121.03911808</v>
       </c>
       <c r="AE4">
         <f>AE3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!AE2</f>
-        <v>189675740.64634836</v>
+        <v>199227889.85103524</v>
       </c>
       <c r="AF4">
         <f>AF3/(1+'Study Parameters'!$C$3) ^ 'LCOF Baseline'!AF2</f>
-        <v>175625685.78365585</v>
+        <v>184470268.38058817</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="B10">
         <f>(SUM(B4:AF4) - SUM(B6:AF6)) / SUM(B8:AF8)</f>
-        <v>11.140505415570722</v>
+        <v>11.705907867765633</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -20050,123 +20050,123 @@
       </c>
       <c r="C14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="D14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="E14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="F14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="G14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="H14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="I14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="J14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="K14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="L14">
         <f>'Cost Components'!$H$26*10^6 + 'Cost Components'!$H$7 * 10^6</f>
-        <v>1989622556.3909774</v>
+        <v>2078622556.3909774</v>
       </c>
       <c r="M14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="N14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="O14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="P14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="Q14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="R14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="S14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="T14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="U14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="V14">
         <f>'Cost Components'!$H$26*10^6 + 'Cost Components'!$H$7 * 10^6</f>
-        <v>1989622556.3909774</v>
+        <v>2078622556.3909774</v>
       </c>
       <c r="W14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="X14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="Y14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="Z14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AA14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AB14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AC14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AD14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AE14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AF14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -20179,123 +20179,123 @@
       </c>
       <c r="C15">
         <f>C14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!C$13</f>
-        <v>1678354218.8805344</v>
+        <v>1760761626.2879419</v>
       </c>
       <c r="D15">
         <f>D14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!D$13</f>
-        <v>1554031684.148643</v>
+        <v>1630334839.1555018</v>
       </c>
       <c r="E15">
         <f>E14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!E$13</f>
-        <v>1438918226.0635583</v>
+        <v>1509569295.5143533</v>
       </c>
       <c r="F15">
         <f>F14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!F$13</f>
-        <v>1332331690.7995908</v>
+        <v>1397749347.6984751</v>
       </c>
       <c r="G15">
         <f>G14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!G$13</f>
-        <v>1233640454.4440656</v>
+        <v>1294212358.9800696</v>
       </c>
       <c r="H15">
         <f>H14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!H$13</f>
-        <v>1142259680.0408013</v>
+        <v>1198344776.8333976</v>
       </c>
       <c r="I15">
         <f>I14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!I$13</f>
-        <v>1057647851.8896309</v>
+        <v>1109578497.0679607</v>
       </c>
       <c r="J15">
         <f>J14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!J$13</f>
-        <v>979303566.56447303</v>
+        <v>1027387497.2851489</v>
       </c>
       <c r="K15">
         <f>K14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!K$13</f>
-        <v>906762561.6337713</v>
+        <v>951284719.70847106</v>
       </c>
       <c r="L15">
         <f>L14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!L$13</f>
-        <v>921580211.86670315</v>
+        <v>962804432.30624008</v>
       </c>
       <c r="M15">
         <f>M14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!M$13</f>
-        <v>777402744.88492048</v>
+        <v>815573319.36597311</v>
       </c>
       <c r="N15">
         <f>N14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!N$13</f>
-        <v>719817356.37492633</v>
+        <v>755160480.89441955</v>
       </c>
       <c r="O15">
         <f>O14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!O$13</f>
-        <v>666497552.19900584</v>
+        <v>699222667.49483287</v>
       </c>
       <c r="P15">
         <f>P14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!P$13</f>
-        <v>617127363.14722753</v>
+        <v>647428395.82854891</v>
       </c>
       <c r="Q15">
         <f>Q14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!Q$13</f>
-        <v>571414225.13632178</v>
+        <v>599470736.87828588</v>
       </c>
       <c r="R15">
         <f>R14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!R$13</f>
-        <v>529087245.49659419</v>
+        <v>555065497.10952401</v>
       </c>
       <c r="S15">
         <f>S14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!S$13</f>
-        <v>489895597.68203163</v>
+        <v>513949534.36067039</v>
       </c>
       <c r="T15">
         <f>T14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!T$13</f>
-        <v>453607034.89077002</v>
+        <v>475879198.48210216</v>
       </c>
       <c r="U15">
         <f>U14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!U$13</f>
-        <v>420006513.78774995</v>
+        <v>440628887.48342788</v>
       </c>
       <c r="V15">
         <f>V14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!V$13</f>
-        <v>426869952.88436061</v>
+        <v>445964743.34332162</v>
       </c>
       <c r="W15">
         <f>W14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!W$13</f>
-        <v>360087889.04985422</v>
+        <v>377768250.58592927</v>
       </c>
       <c r="X15">
         <f>X14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!X$13</f>
-        <v>333414712.08319831</v>
+        <v>349785417.20919371</v>
       </c>
       <c r="Y15">
         <f>Y14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!Y$13</f>
-        <v>308717326.0029614</v>
+        <v>323875386.30480897</v>
       </c>
       <c r="Z15">
         <f>Z14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!Z$13</f>
-        <v>285849375.92866796</v>
+        <v>299884616.94889718</v>
       </c>
       <c r="AA15">
         <f>AA14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!AA$13</f>
-        <v>264675348.08209991</v>
+        <v>277670941.61934924</v>
       </c>
       <c r="AB15">
         <f>AB14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!AB$13</f>
-        <v>245069766.74268514</v>
+        <v>257102723.72161967</v>
       </c>
       <c r="AC15">
         <f>AC14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!AC$13</f>
-        <v>226916450.68767142</v>
+        <v>238058077.52001822</v>
       </c>
       <c r="AD15">
         <f>AD14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!AD$13</f>
-        <v>210107824.71080688</v>
+        <v>220424145.85186872</v>
       </c>
       <c r="AE15">
         <f>AE14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!AE$13</f>
-        <v>194544282.13963598</v>
+        <v>204096431.34432286</v>
       </c>
       <c r="AF15">
         <f>AF14/(1+'Study Parameters'!$C$3) ^'LCOF Baseline'!AF$13</f>
-        <v>180133594.573737</v>
+        <v>188978177.17066929</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="B21">
         <f>(SUM(B15:AF15) - SUM(B17:AF17)) / SUM(B19:AF19)</f>
-        <v>11.428679860916159</v>
+        <v>11.994082313111065</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
@@ -20932,123 +20932,123 @@
       </c>
       <c r="C25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="D25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="E25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="F25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="G25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="H25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="I25">
         <f>'Cost Components'!$N$26 * 10^6 + 'Cost Components'!$N$7 * 10^6</f>
-        <v>2102761904.7619045</v>
+        <v>2191761904.7619047</v>
       </c>
       <c r="J25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="K25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="L25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="M25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="N25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="O25">
         <f>'Cost Components'!$N$26 * 10^6 + 'Cost Components'!$N$7 * 10^6</f>
-        <v>2102761904.7619045</v>
+        <v>2191761904.7619047</v>
       </c>
       <c r="P25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="Q25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="R25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="S25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="T25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="U25">
         <f>'Cost Components'!$N$26 * 10^6 + 'Cost Components'!$N$7 * 10^6</f>
-        <v>2102761904.7619045</v>
+        <v>2191761904.7619047</v>
       </c>
       <c r="V25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="W25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="X25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="Y25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="Z25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="AA25">
         <f>'Cost Components'!$N$26* 10^6 + 'Cost Components'!$N$7 * 10^6</f>
-        <v>2102761904.7619045</v>
+        <v>2191761904.7619047</v>
       </c>
       <c r="AB25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="AC25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="AD25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="AE25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="AF25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
@@ -21061,123 +21061,123 @@
       </c>
       <c r="C26">
         <f>C25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!C$24</f>
-        <v>1599779541.4462078</v>
+        <v>1682186948.853615</v>
       </c>
       <c r="D26">
         <f>D25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!D$24</f>
-        <v>1481277353.190933</v>
+        <v>1557580508.1977918</v>
       </c>
       <c r="E26">
         <f>E25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!E$24</f>
-        <v>1371553104.8064194</v>
+        <v>1442204174.2572145</v>
       </c>
       <c r="F26">
         <f>F25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!F$24</f>
-        <v>1269956578.5244622</v>
+        <v>1335374235.4233468</v>
       </c>
       <c r="G26">
         <f>G25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!G$24</f>
-        <v>1175885720.8559837</v>
+        <v>1236457625.3919876</v>
       </c>
       <c r="H26">
         <f>H25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!H$24</f>
-        <v>1088783074.8666513</v>
+        <v>1144868171.6592476</v>
       </c>
       <c r="I26">
         <f>I25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!I$24</f>
-        <v>1226941374.9516811</v>
+        <v>1278872020.1300111</v>
       </c>
       <c r="J26">
         <f>J25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!J$24</f>
-        <v>933455996.97072303</v>
+        <v>981539927.69139886</v>
       </c>
       <c r="K26">
         <f>K25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!K$24</f>
-        <v>864311108.30622494</v>
+        <v>908833266.38092482</v>
       </c>
       <c r="L26">
         <f>L25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!L$24</f>
-        <v>800288063.24650455</v>
+        <v>841512283.68604147</v>
       </c>
       <c r="M26">
         <f>M25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!M$24</f>
-        <v>741007465.96898568</v>
+        <v>779178040.45003843</v>
       </c>
       <c r="N26">
         <f>N25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!N$24</f>
-        <v>686118024.04535711</v>
+        <v>721461148.56485033</v>
       </c>
       <c r="O26">
         <f>O25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!O$24</f>
-        <v>773181188.46074426</v>
+        <v>805906303.75657141</v>
       </c>
       <c r="P26">
         <f>P25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!P$24</f>
-        <v>588235617.32283688</v>
+        <v>618536650.00415826</v>
       </c>
       <c r="Q26">
         <f>Q25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Q$24</f>
-        <v>544662608.63225639</v>
+        <v>572719120.37422061</v>
       </c>
       <c r="R26">
         <f>R25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!R$24</f>
-        <v>504317230.21505219</v>
+        <v>530295481.82798201</v>
       </c>
       <c r="S26">
         <f>S25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!S$24</f>
-        <v>466960398.34727055</v>
+        <v>491014335.02590925</v>
       </c>
       <c r="T26">
         <f>T25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!T$24</f>
-        <v>432370739.21043563</v>
+        <v>454642902.80176777</v>
       </c>
       <c r="U26">
         <f>U25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!U$24</f>
-        <v>487235301.0453425</v>
+        <v>507857674.7410205</v>
       </c>
       <c r="V26">
         <f>V25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!V$24</f>
-        <v>370688219.48768485</v>
+        <v>389783009.94664592</v>
       </c>
       <c r="W26">
         <f>W25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!W$24</f>
-        <v>343229832.85896742</v>
+        <v>360910194.39504248</v>
       </c>
       <c r="X26">
         <f>X25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!X$24</f>
-        <v>317805400.79534018</v>
+        <v>334176105.92133558</v>
       </c>
       <c r="Y26">
         <f>Y25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Y$24</f>
-        <v>294264259.99568534</v>
+        <v>309422320.29753292</v>
       </c>
       <c r="Z26">
         <f>Z25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Z$24</f>
-        <v>272466907.40341234</v>
+        <v>286502148.42364162</v>
       </c>
       <c r="AA26">
         <f>AA25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AA$24</f>
-        <v>307040887.86402065</v>
+        <v>320036481.40126997</v>
       </c>
       <c r="AB26">
         <f>AB25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AB$24</f>
-        <v>233596456.96451676</v>
+        <v>245629413.94345129</v>
       </c>
       <c r="AC26">
         <f>AC25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AC$24</f>
-        <v>216293015.70788589</v>
+        <v>227434642.54023269</v>
       </c>
       <c r="AD26">
         <f>AD25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AD$24</f>
-        <v>200271310.84063506</v>
+        <v>210587631.98169693</v>
       </c>
       <c r="AE26">
         <f>AE25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AE$24</f>
-        <v>185436398.92651394</v>
+        <v>194988548.13120085</v>
       </c>
       <c r="AF26">
         <f>AF25/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AF$24</f>
-        <v>171700369.37640178</v>
+        <v>180544951.97333407</v>
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="B32">
         <f>(SUM(B26:AF26) - SUM(B28:AF28)) / SUM(B30:AF30)</f>
-        <v>11.255461144747709</v>
+        <v>11.820863596942624</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.25">
@@ -21814,123 +21814,123 @@
       </c>
       <c r="C36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="D36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="E36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="F36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="G36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="H36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="I36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="J36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="K36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="L36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="M36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="N36">
         <f>'Cost Components'!$T$26 * 10^6 + 'Cost Components'!$T$7 * 10^6</f>
-        <v>962839999.99999988</v>
+        <v>1005839999.9999999</v>
       </c>
       <c r="O36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="P36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="Q36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="R36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="S36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="T36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="U36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="V36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="W36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="X36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="Y36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="Z36">
         <f>'Cost Components'!$T$26 * 10^6 + 'Cost Components'!$T$7 * 10^6</f>
-        <v>962839999.99999988</v>
+        <v>1005839999.9999999</v>
       </c>
       <c r="AA36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="AB36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="AC36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="AD36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="AE36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="AF36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
@@ -21943,123 +21943,123 @@
       </c>
       <c r="C37">
         <f>C36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!C$35</f>
-        <v>827629629.62962949</v>
+        <v>867444444.4444443</v>
       </c>
       <c r="D37">
         <f>D36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!D$35</f>
-        <v>766323731.13854575</v>
+        <v>803189300.41152251</v>
       </c>
       <c r="E37">
         <f>E36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!E$35</f>
-        <v>709559010.31346834</v>
+        <v>743693796.67733562</v>
       </c>
       <c r="F37">
         <f>F36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!F$35</f>
-        <v>656999083.62358165</v>
+        <v>688605367.2938292</v>
       </c>
       <c r="G37">
         <f>G36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!G$35</f>
-        <v>608332484.83664966</v>
+        <v>637597562.3091011</v>
       </c>
       <c r="H37">
         <f>H36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!H$35</f>
-        <v>563270819.29319406</v>
+        <v>590368113.24916756</v>
       </c>
       <c r="I37">
         <f>I36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!I$35</f>
-        <v>521547054.90110564</v>
+        <v>546637141.89737737</v>
       </c>
       <c r="J37">
         <f>J36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!J$35</f>
-        <v>482913939.72324598</v>
+        <v>506145501.75683093</v>
       </c>
       <c r="K37">
         <f>K36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!K$35</f>
-        <v>447142536.78078324</v>
+        <v>468653242.36743599</v>
       </c>
       <c r="L37">
         <f>L36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!L$35</f>
-        <v>414020867.38961411</v>
+        <v>433938187.37725556</v>
       </c>
       <c r="M37">
         <f>M36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!M$35</f>
-        <v>383352654.99038345</v>
+        <v>401794617.94190329</v>
       </c>
       <c r="N37">
         <f>N36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!N$35</f>
-        <v>382357011.37470621</v>
+        <v>399432902.9964838</v>
       </c>
       <c r="O37">
         <f>O36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!O$35</f>
-        <v>328663112.98901182</v>
+        <v>344474123.74991703</v>
       </c>
       <c r="P37">
         <f>P36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!P$35</f>
-        <v>304317697.21204793</v>
+        <v>318957521.99066389</v>
       </c>
       <c r="Q37">
         <f>Q36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Q$35</f>
-        <v>281775645.56671107</v>
+        <v>295331038.88024431</v>
       </c>
       <c r="R37">
         <f>R36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!R$35</f>
-        <v>260903375.52473247</v>
+        <v>273454665.62985587</v>
       </c>
       <c r="S37">
         <f>S36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!S$35</f>
-        <v>241577199.55993745</v>
+        <v>253198764.47208875</v>
       </c>
       <c r="T37">
         <f>T36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!T$35</f>
-        <v>223682592.18512726</v>
+        <v>234443300.43711919</v>
       </c>
       <c r="U37">
         <f>U36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!U$35</f>
-        <v>207113511.28252521</v>
+        <v>217077130.03436959</v>
       </c>
       <c r="V37">
         <f>V36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!V$35</f>
-        <v>191771769.70604187</v>
+        <v>200997342.62441629</v>
       </c>
       <c r="W37">
         <f>W36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!W$35</f>
-        <v>177566453.43152025</v>
+        <v>186108650.57816324</v>
       </c>
       <c r="X37">
         <f>X36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!X$35</f>
-        <v>164413382.80696318</v>
+        <v>172322824.60941038</v>
       </c>
       <c r="Y37">
         <f>Y36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Y$35</f>
-        <v>152234613.71015108</v>
+        <v>159558170.93463925</v>
       </c>
       <c r="Z37">
         <f>Z36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Z$35</f>
-        <v>151839229.93165761</v>
+        <v>158620301.43581331</v>
       </c>
       <c r="AA37">
         <f>AA36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AA$35</f>
-        <v>130516644.12735859</v>
+        <v>136795414.03861386</v>
       </c>
       <c r="AB37">
         <f>AB36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AB$35</f>
-        <v>120848744.56236906</v>
+        <v>126662420.40612397</v>
       </c>
       <c r="AC37">
         <f>AC36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AC$35</f>
-        <v>111896985.70589729</v>
+        <v>117280018.89455922</v>
       </c>
       <c r="AD37">
         <f>AD36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AD$35</f>
-        <v>103608320.09805304</v>
+        <v>108592610.08755483</v>
       </c>
       <c r="AE37">
         <f>AE36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AE$35</f>
-        <v>95933629.720419481</v>
+        <v>100548713.04403225</v>
       </c>
       <c r="AF37">
         <f>AF36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AF$35</f>
-        <v>88827434.926314324</v>
+        <v>93100660.225955769</v>
       </c>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
@@ -22580,7 +22580,7 @@
       </c>
       <c r="B43">
         <f>(SUM(B37:AF37) - SUM(B39:AF39)) / SUM(B41:AF41)</f>
-        <v>5.4046364232797934</v>
+        <v>5.677808394564976</v>
       </c>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.25">
@@ -22696,123 +22696,123 @@
       </c>
       <c r="C47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="D47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="E47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="F47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="G47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="H47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="I47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="J47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="K47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="L47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="M47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="N47">
         <f>'Cost Components'!$Z$26* 10^6 + 'Cost Components'!$Z$7 * 10^6</f>
-        <v>937246736.84210527</v>
+        <v>980246736.84210527</v>
       </c>
       <c r="O47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="P47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="Q47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="R47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="S47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="T47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="U47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="V47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="W47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="X47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="Y47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="Z47">
         <f>'Cost Components'!$Z$26 * 10^6 + 'Cost Components'!$Z$7 * 10^6</f>
-        <v>937246736.84210527</v>
+        <v>980246736.84210527</v>
       </c>
       <c r="AA47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="AB47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="AC47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="AD47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="AE47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="AF47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.25">
@@ -22825,123 +22825,123 @@
       </c>
       <c r="C48">
         <f>C47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!C$46</f>
-        <v>803932163.74268997</v>
+        <v>843746978.55750477</v>
       </c>
       <c r="D48">
         <f>D47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!D$46</f>
-        <v>744381633.09508336</v>
+        <v>781247202.36805999</v>
       </c>
       <c r="E48">
         <f>E47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!E$46</f>
-        <v>689242252.8658179</v>
+        <v>723377039.22968519</v>
       </c>
       <c r="F48">
         <f>F47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!F$46</f>
-        <v>638187271.17205358</v>
+        <v>669793554.84230101</v>
       </c>
       <c r="G48">
         <f>G47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!G$46</f>
-        <v>590914139.9741236</v>
+        <v>620179217.44657505</v>
       </c>
       <c r="H48">
         <f>H47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!H$46</f>
-        <v>547142722.19826257</v>
+        <v>574240016.15423608</v>
       </c>
       <c r="I48">
         <f>I47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!I$46</f>
-        <v>506613631.6650579</v>
+        <v>531703718.66132963</v>
       </c>
       <c r="J48">
         <f>J47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!J$46</f>
-        <v>469086695.98616475</v>
+        <v>492318258.0197497</v>
       </c>
       <c r="K48">
         <f>K47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!K$46</f>
-        <v>434339533.32052284</v>
+        <v>455850238.9071756</v>
       </c>
       <c r="L48">
         <f>L47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!L$46</f>
-        <v>402166234.55603969</v>
+        <v>422083554.54368109</v>
       </c>
       <c r="M48">
         <f>M47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!M$46</f>
-        <v>372376143.10744417</v>
+        <v>390818106.05896395</v>
       </c>
       <c r="N48">
         <f>N47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!N$46</f>
-        <v>372193574.44605869</v>
+        <v>389269466.06783628</v>
       </c>
       <c r="O48">
         <f>O47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!O$46</f>
-        <v>319252523.24026418</v>
+        <v>335063534.00116938</v>
       </c>
       <c r="P48">
         <f>P47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!P$46</f>
-        <v>295604188.18542969</v>
+        <v>310244012.96404564</v>
       </c>
       <c r="Q48">
         <f>Q47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Q$46</f>
-        <v>273707581.65317565</v>
+        <v>287262974.9667089</v>
       </c>
       <c r="R48">
         <f>R47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!R$46</f>
-        <v>253432945.97516266</v>
+        <v>265984236.08028606</v>
       </c>
       <c r="S48">
         <f>S47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!S$46</f>
-        <v>234660135.16218764</v>
+        <v>246281700.07433891</v>
       </c>
       <c r="T48">
         <f>T47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!T$46</f>
-        <v>217277902.92795148</v>
+        <v>228038611.17994341</v>
       </c>
       <c r="U48">
         <f>U47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!U$46</f>
-        <v>201183243.4518069</v>
+        <v>211146862.20365131</v>
       </c>
       <c r="V48">
         <f>V47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!V$46</f>
-        <v>186280780.97389531</v>
+        <v>195506353.89226973</v>
       </c>
       <c r="W48">
         <f>W47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!W$46</f>
-        <v>172482204.60545862</v>
+        <v>181024401.7521016</v>
       </c>
       <c r="X48">
         <f>X47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!X$46</f>
-        <v>159705745.00505424</v>
+        <v>167615186.80750147</v>
       </c>
       <c r="Y48">
         <f>Y47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Y$46</f>
-        <v>147875689.81949466</v>
+        <v>155199247.04398283</v>
       </c>
       <c r="Z48">
         <f>Z47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Z$46</f>
-        <v>147803189.29216093</v>
+        <v>154584260.79631662</v>
       </c>
       <c r="AA48">
         <f>AA47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AA$46</f>
-        <v>126779569.46115796</v>
+        <v>133058339.37241323</v>
       </c>
       <c r="AB48">
         <f>AB47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AB$46</f>
-        <v>117388490.24181293</v>
+        <v>123202166.08556782</v>
       </c>
       <c r="AC48">
         <f>AC47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AC$46</f>
-        <v>108693046.52019715</v>
+        <v>114076079.70885909</v>
       </c>
       <c r="AD48">
         <f>AD47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AD$46</f>
-        <v>100641709.74092329</v>
+        <v>105625999.73042509</v>
       </c>
       <c r="AE48">
         <f>AE47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AE$46</f>
-        <v>93186768.278632671</v>
+        <v>97801851.602245435</v>
       </c>
       <c r="AF48">
         <f>AF47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AF$46</f>
-        <v>86284044.702437654</v>
+        <v>90557270.002079099</v>
       </c>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.25">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="B54">
         <f>(SUM(B48:AF48) - SUM(B50:AF50)) / SUM(B52:AF52)</f>
-        <v>5.2420466058736945</v>
+        <v>5.5152185771588691</v>
       </c>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.25">
@@ -23578,123 +23578,123 @@
       </c>
       <c r="C58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="D58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="E58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="F58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="G58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="H58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="I58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="J58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="K58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="L58">
         <f>'Cost Components'!$AF$26*10^6 + 'Cost Components'!$AF$7 * 10^6</f>
-        <v>889404631.57894742</v>
+        <v>932404631.57894742</v>
       </c>
       <c r="M58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="N58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="O58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="P58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="Q58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="R58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="S58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="T58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="U58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="V58">
         <f>'Cost Components'!$AF$26*10^6 + 'Cost Components'!$AF$7 * 10^6</f>
-        <v>889404631.57894742</v>
+        <v>932404631.57894742</v>
       </c>
       <c r="W58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="X58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="Y58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="Z58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AA58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AB58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AC58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AD58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AE58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AF58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.25">
@@ -23707,123 +23707,123 @@
       </c>
       <c r="C59">
         <f>C58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!C$57</f>
-        <v>758707992.20272911</v>
+        <v>798522807.01754391</v>
       </c>
       <c r="D59">
         <f>D58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!D$57</f>
-        <v>702507400.18771207</v>
+        <v>739372969.46068871</v>
       </c>
       <c r="E59">
         <f>E58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!E$57</f>
-        <v>650469814.98862231</v>
+        <v>684604601.35248959</v>
       </c>
       <c r="F59">
         <f>F58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!F$57</f>
-        <v>602286865.73020577</v>
+        <v>633893149.40045321</v>
       </c>
       <c r="G59">
         <f>G58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!G$57</f>
-        <v>557673023.82426453</v>
+        <v>586938101.29671597</v>
       </c>
       <c r="H59">
         <f>H58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!H$57</f>
-        <v>516363910.94839305</v>
+        <v>543461204.90436661</v>
       </c>
       <c r="I59">
         <f>I58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!I$57</f>
-        <v>478114732.35962319</v>
+        <v>503204819.35589492</v>
       </c>
       <c r="J59">
         <f>J58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!J$57</f>
-        <v>442698826.25891036</v>
+        <v>465930388.29249531</v>
       </c>
       <c r="K59">
         <f>K58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!K$57</f>
-        <v>409906320.61010218</v>
+        <v>431417026.19675487</v>
       </c>
       <c r="L59">
         <f>L58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!L$57</f>
-        <v>411966433.61972618</v>
+        <v>431883753.60736758</v>
       </c>
       <c r="M59">
         <f>M58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!M$57</f>
-        <v>351428601.34610951</v>
+        <v>369870564.29762936</v>
       </c>
       <c r="N59">
         <f>N58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!N$57</f>
-        <v>325396853.0982495</v>
+        <v>342472744.72002715</v>
       </c>
       <c r="O59">
         <f>O58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!O$57</f>
-        <v>301293382.49837917</v>
+        <v>317104393.25928438</v>
       </c>
       <c r="P59">
         <f>P58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!P$57</f>
-        <v>278975354.16516584</v>
+        <v>293615178.94378179</v>
       </c>
       <c r="Q59">
         <f>Q58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Q$57</f>
-        <v>258310513.11589429</v>
+        <v>271865906.42942756</v>
       </c>
       <c r="R59">
         <f>R58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!R$57</f>
-        <v>239176401.03323546</v>
+        <v>251727691.13835886</v>
       </c>
       <c r="S59">
         <f>S58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!S$57</f>
-        <v>221459630.58632913</v>
+        <v>233081195.49848044</v>
       </c>
       <c r="T59">
         <f>T58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!T$57</f>
-        <v>205055213.5058603</v>
+        <v>215815921.75785223</v>
       </c>
       <c r="U59">
         <f>U58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!U$57</f>
-        <v>189865938.43135211</v>
+        <v>199829557.18319649</v>
       </c>
       <c r="V59">
         <f>V58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!V$57</f>
-        <v>190820169.3621285</v>
+        <v>200045742.28050295</v>
       </c>
       <c r="W59">
         <f>W58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!W$57</f>
-        <v>162779439.67022642</v>
+        <v>171321636.81686941</v>
       </c>
       <c r="X59">
         <f>X58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!X$57</f>
-        <v>150721703.39835778</v>
+        <v>158631145.20080501</v>
       </c>
       <c r="Y59">
         <f>Y58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Y$57</f>
-        <v>139557132.77625722</v>
+        <v>146880690.00074536</v>
       </c>
       <c r="Z59">
         <f>Z58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Z$57</f>
-        <v>129219567.38542333</v>
+        <v>136000638.88957903</v>
       </c>
       <c r="AA59">
         <f>AA58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AA$57</f>
-        <v>119647747.57909566</v>
+        <v>125926517.49035095</v>
       </c>
       <c r="AB59">
         <f>AB58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AB$57</f>
-        <v>110784951.46212563</v>
+        <v>116598627.30588052</v>
       </c>
       <c r="AC59">
         <f>AC58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AC$57</f>
-        <v>102578658.76122743</v>
+        <v>107961691.94988936</v>
       </c>
       <c r="AD59">
         <f>AD58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AD$57</f>
-        <v>94980239.593729094</v>
+        <v>99964529.583230883</v>
       </c>
       <c r="AE59">
         <f>AE58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AE$57</f>
-        <v>87944666.290489897</v>
+        <v>92559749.614102662</v>
       </c>
       <c r="AF59">
         <f>AF58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AF$57</f>
-        <v>81430246.565268412</v>
+        <v>85703471.864909872</v>
       </c>
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.25">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="B65">
         <f>(SUM(B59:AF59) - SUM(B61:AF61)) / SUM(B63:AF63)</f>
-        <v>4.9058927958421643</v>
+        <v>5.179064767127346</v>
       </c>
     </row>
   </sheetData>
@@ -24479,123 +24479,123 @@
       </c>
       <c r="C3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="D3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="E3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="F3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="G3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="H3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="I3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="J3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="K3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="L3">
         <f>'Cost Components'!$B$26 * 10^6 + 'Cost Components'!$B$7*10^6</f>
-        <v>1944261016.9491527</v>
+        <v>2033261016.9491527</v>
       </c>
       <c r="M3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="N3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="O3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="P3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="Q3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="R3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="S3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="T3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="U3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="V3">
         <f>'Cost Components'!$B$26 * 10^6 + 'Cost Components'!$B$7*10^6</f>
-        <v>1944261016.9491527</v>
+        <v>2033261016.9491527</v>
       </c>
       <c r="W3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="X3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="Y3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="Z3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AA3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AB3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AC3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AD3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AE3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
       <c r="AF3">
         <f>'Cost Components'!$B$26 * 10^6</f>
-        <v>1767261016.9491527</v>
+        <v>1856261016.9491527</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -24608,123 +24608,123 @@
       </c>
       <c r="C4">
         <f>C3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!C2</f>
-        <v>1651645810.2328529</v>
+        <v>1734823380.3263109</v>
       </c>
       <c r="D4">
         <f>D3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!D2</f>
-        <v>1543594215.1708906</v>
+        <v>1621330261.9872065</v>
       </c>
       <c r="E4">
         <f>E3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!E2</f>
-        <v>1442611416.0475612</v>
+        <v>1515261927.090847</v>
       </c>
       <c r="F4">
         <f>F3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!F2</f>
-        <v>1348234968.268749</v>
+        <v>1416132642.1409786</v>
       </c>
       <c r="G4">
         <f>G3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!G2</f>
-        <v>1260032680.6249988</v>
+        <v>1323488450.5990453</v>
       </c>
       <c r="H4">
         <f>H3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!H2</f>
-        <v>1177600636.0981297</v>
+        <v>1236905094.0177994</v>
       </c>
       <c r="I4">
         <f>I3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!I2</f>
-        <v>1100561342.1477849</v>
+        <v>1155986069.1755135</v>
       </c>
       <c r="J4">
         <f>J3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!J2</f>
-        <v>1028562002.0072756</v>
+        <v>1080360812.3135641</v>
       </c>
       <c r="K4">
         <f>K3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!K2</f>
-        <v>961272899.07222009</v>
+        <v>1009683002.1622093</v>
       </c>
       <c r="L4">
         <f>L3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!L2</f>
-        <v>988363711.69122839</v>
+        <v>1033606798.6912183</v>
       </c>
       <c r="M4">
         <f>M3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!M2</f>
-        <v>839612978.48914313</v>
+        <v>881896237.36763835</v>
       </c>
       <c r="N4">
         <f>N3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!N2</f>
-        <v>784685026.62536764</v>
+        <v>824202090.99779308</v>
       </c>
       <c r="O4">
         <f>O3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!O2</f>
-        <v>733350492.17324066</v>
+        <v>770282328.03532052</v>
       </c>
       <c r="P4">
         <f>P3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!P2</f>
-        <v>685374291.75069225</v>
+        <v>719890026.20123422</v>
       </c>
       <c r="Q4">
         <f>Q3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!Q2</f>
-        <v>640536721.2623291</v>
+        <v>672794417.01049912</v>
       </c>
       <c r="R4">
         <f>R3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!R2</f>
-        <v>598632449.77787781</v>
+        <v>628779828.98177493</v>
       </c>
       <c r="S4">
         <f>S3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!S2</f>
-        <v>559469579.23166144</v>
+        <v>587644699.98296726</v>
       </c>
       <c r="T4">
         <f>T3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!T2</f>
-        <v>522868765.63706678</v>
+        <v>549200654.18968904</v>
       </c>
       <c r="U4">
         <f>U3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!U2</f>
-        <v>488662397.79165119</v>
+        <v>513271639.42961586</v>
       </c>
       <c r="V4">
         <f>V3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!V2</f>
-        <v>502433993.20987833</v>
+        <v>525433284.4603126</v>
       </c>
       <c r="W4">
         <f>W3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!W2</f>
-        <v>426816663.28207809</v>
+        <v>448311328.00211012</v>
       </c>
       <c r="X4">
         <f>X3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!X2</f>
-        <v>398894077.83371782</v>
+        <v>418982549.53468239</v>
       </c>
       <c r="Y4">
         <f>Y3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!Y2</f>
-        <v>372798203.58291382</v>
+        <v>391572476.2006377</v>
       </c>
       <c r="Z4">
         <f>Z3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!Z2</f>
-        <v>348409536.05879796</v>
+        <v>365955585.23424083</v>
       </c>
       <c r="AA4">
         <f>AA3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!AA2</f>
-        <v>325616388.83999807</v>
+        <v>342014565.63947743</v>
       </c>
       <c r="AB4">
         <f>AB3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!AB2</f>
-        <v>304314382.09345621</v>
+        <v>319639780.97147423</v>
       </c>
       <c r="AC4">
         <f>AC3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!AC2</f>
-        <v>284405964.57332349</v>
+        <v>298728767.26305997</v>
       </c>
       <c r="AD4">
         <f>AD3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!AD2</f>
-        <v>265799966.89095658</v>
+        <v>279185763.79725236</v>
       </c>
       <c r="AE4">
         <f>AE3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!AE2</f>
-        <v>248411184.01023978</v>
+        <v>260921274.57687137</v>
       </c>
       <c r="AF4">
         <f>AF3/(1+Inputs!$C$5) ^ 'LCOF Baseline'!AF2</f>
-        <v>232159985.05629885</v>
+        <v>243851658.48305735</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -25245,7 +25245,7 @@
       </c>
       <c r="B10">
         <f>(SUM(B4:AF4) - SUM(B6:AF6)) / SUM(B8:AF8)</f>
-        <v>11.084702911966531</v>
+        <v>11.650105364161435</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -25361,123 +25361,123 @@
       </c>
       <c r="C14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="D14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="E14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="F14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="G14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="H14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="I14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="J14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="K14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="L14">
         <f>'Cost Components'!$H$26*10^6 + 'Cost Components'!$H$7 * 10^6</f>
-        <v>1989622556.3909774</v>
+        <v>2078622556.3909774</v>
       </c>
       <c r="M14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="N14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="O14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="P14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="Q14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="R14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="S14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="T14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="U14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="V14">
         <f>'Cost Components'!$H$26*10^6 + 'Cost Components'!$H$7 * 10^6</f>
-        <v>1989622556.3909774</v>
+        <v>2078622556.3909774</v>
       </c>
       <c r="W14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="X14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="Y14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="Z14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AA14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AB14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AC14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AD14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AE14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
       <c r="AF14">
         <f>'Cost Components'!$H$26*10^6</f>
-        <v>1812622556.3909774</v>
+        <v>1901622556.3909774</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -25490,123 +25490,123 @@
       </c>
       <c r="C15">
         <f>C14/(1+Inputs!$C$5) ^'LCOF Baseline'!C$13</f>
-        <v>1694039772.328016</v>
+        <v>1777217342.421474</v>
       </c>
       <c r="D15">
         <f>D14/(1+Inputs!$C$5) ^'LCOF Baseline'!D$13</f>
-        <v>1583214740.4934731</v>
+        <v>1660950787.3097889</v>
       </c>
       <c r="E15">
         <f>E14/(1+Inputs!$C$5) ^'LCOF Baseline'!E$13</f>
-        <v>1479639944.3864233</v>
+        <v>1552290455.4297092</v>
       </c>
       <c r="F15">
         <f>F14/(1+Inputs!$C$5) ^'LCOF Baseline'!F$13</f>
-        <v>1382841069.5200219</v>
+        <v>1450738743.3922517</v>
       </c>
       <c r="G15">
         <f>G14/(1+Inputs!$C$5) ^'LCOF Baseline'!G$13</f>
-        <v>1292374831.3271232</v>
+        <v>1355830601.3011696</v>
       </c>
       <c r="H15">
         <f>H14/(1+Inputs!$C$5) ^'LCOF Baseline'!H$13</f>
-        <v>1207826945.1655357</v>
+        <v>1267131403.0852053</v>
       </c>
       <c r="I15">
         <f>I14/(1+Inputs!$C$5) ^'LCOF Baseline'!I$13</f>
-        <v>1128810229.1266689</v>
+        <v>1184234956.1543975</v>
       </c>
       <c r="J15">
         <f>J14/(1+Inputs!$C$5) ^'LCOF Baseline'!J$13</f>
-        <v>1054962830.9595037</v>
+        <v>1106761641.2657921</v>
       </c>
       <c r="K15">
         <f>K14/(1+Inputs!$C$5) ^'LCOF Baseline'!K$13</f>
-        <v>985946570.99019015</v>
+        <v>1034356674.0801793</v>
       </c>
       <c r="L15">
         <f>L14/(1+Inputs!$C$5) ^'LCOF Baseline'!L$13</f>
-        <v>1011423218.156621</v>
+        <v>1056666305.1566108</v>
       </c>
       <c r="M15">
         <f>M14/(1+Inputs!$C$5) ^'LCOF Baseline'!M$13</f>
-        <v>861163919.11100543</v>
+        <v>903447177.98950064</v>
       </c>
       <c r="N15">
         <f>N14/(1+Inputs!$C$5) ^'LCOF Baseline'!N$13</f>
-        <v>804826092.6271081</v>
+        <v>844343156.99953353</v>
       </c>
       <c r="O15">
         <f>O14/(1+Inputs!$C$5) ^'LCOF Baseline'!O$13</f>
-        <v>752173918.34309161</v>
+        <v>789105754.20517147</v>
       </c>
       <c r="P15">
         <f>P14/(1+Inputs!$C$5) ^'LCOF Baseline'!P$13</f>
-        <v>702966278.82531929</v>
+        <v>737482013.27586114</v>
       </c>
       <c r="Q15">
         <f>Q14/(1+Inputs!$C$5) ^'LCOF Baseline'!Q$13</f>
-        <v>656977830.67786837</v>
+        <v>689235526.42603838</v>
       </c>
       <c r="R15">
         <f>R14/(1+Inputs!$C$5) ^'LCOF Baseline'!R$13</f>
-        <v>613997972.59613872</v>
+        <v>644145351.80003595</v>
       </c>
       <c r="S15">
         <f>S14/(1+Inputs!$C$5) ^'LCOF Baseline'!S$13</f>
-        <v>573829880.93097079</v>
+        <v>602005001.68227661</v>
       </c>
       <c r="T15">
         <f>T14/(1+Inputs!$C$5) ^'LCOF Baseline'!T$13</f>
-        <v>536289608.34670168</v>
+        <v>562621496.89932394</v>
       </c>
       <c r="U15">
         <f>U14/(1+Inputs!$C$5) ^'LCOF Baseline'!U$13</f>
-        <v>501205241.44551557</v>
+        <v>525814483.08348024</v>
       </c>
       <c r="V15">
         <f>V14/(1+Inputs!$C$5) ^'LCOF Baseline'!V$13</f>
-        <v>514156276.99853665</v>
+        <v>537155568.24897099</v>
       </c>
       <c r="W15">
         <f>W14/(1+Inputs!$C$5) ^'LCOF Baseline'!W$13</f>
-        <v>437772068.69203907</v>
+        <v>459266733.41207117</v>
       </c>
       <c r="X15">
         <f>X14/(1+Inputs!$C$5) ^'LCOF Baseline'!X$13</f>
-        <v>409132774.4785412</v>
+        <v>429221246.17950577</v>
       </c>
       <c r="Y15">
         <f>Y14/(1+Inputs!$C$5) ^'LCOF Baseline'!Y$13</f>
-        <v>382367078.95190769</v>
+        <v>401141351.56963158</v>
       </c>
       <c r="Z15">
         <f>Z14/(1+Inputs!$C$5) ^'LCOF Baseline'!Z$13</f>
-        <v>357352410.23542774</v>
+        <v>374898459.41087061</v>
       </c>
       <c r="AA15">
         <f>AA14/(1+Inputs!$C$5) ^'LCOF Baseline'!AA$13</f>
-        <v>333974215.17329693</v>
+        <v>350372391.97277623</v>
       </c>
       <c r="AB15">
         <f>AB14/(1+Inputs!$C$5) ^'LCOF Baseline'!AB$13</f>
-        <v>312125434.74139899</v>
+        <v>327450833.61941707</v>
       </c>
       <c r="AC15">
         <f>AC14/(1+Inputs!$C$5) ^'LCOF Baseline'!AC$13</f>
-        <v>291706013.77700835</v>
+        <v>306028816.46674484</v>
       </c>
       <c r="AD15">
         <f>AD14/(1+Inputs!$C$5) ^'LCOF Baseline'!AD$13</f>
-        <v>272622442.78225088</v>
+        <v>286008239.68854666</v>
       </c>
       <c r="AE15">
         <f>AE14/(1+Inputs!$C$5) ^'LCOF Baseline'!AE$13</f>
-        <v>254787329.70303819</v>
+        <v>267297420.26966977</v>
       </c>
       <c r="AF15">
         <f>AF14/(1+Inputs!$C$5) ^'LCOF Baseline'!AF$13</f>
-        <v>238118999.7224656</v>
+        <v>249810673.1492241</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="B21">
         <f>(SUM(B15:AF15) - SUM(B17:AF17)) / SUM(B19:AF19)</f>
-        <v>11.37287735731196</v>
+        <v>11.938279809506865</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
@@ -26243,123 +26243,123 @@
       </c>
       <c r="C25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="D25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="E25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="F25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="G25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="H25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="I25">
         <f>'Cost Components'!$N$26 * 10^6 + 'Cost Components'!$N$7 * 10^6</f>
-        <v>2102761904.7619045</v>
+        <v>2191761904.7619047</v>
       </c>
       <c r="J25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="K25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="L25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="M25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="N25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="O25">
         <f>'Cost Components'!$N$26 * 10^6 + 'Cost Components'!$N$7 * 10^6</f>
-        <v>2102761904.7619045</v>
+        <v>2191761904.7619047</v>
       </c>
       <c r="P25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="Q25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="R25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="S25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="T25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="U25">
         <f>'Cost Components'!$N$26 * 10^6 + 'Cost Components'!$N$7 * 10^6</f>
-        <v>2102761904.7619045</v>
+        <v>2191761904.7619047</v>
       </c>
       <c r="V25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="W25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="X25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="Y25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="Z25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="AA25">
         <f>'Cost Components'!$N$26* 10^6 + 'Cost Components'!$N$7 * 10^6</f>
-        <v>2102761904.7619045</v>
+        <v>2191761904.7619047</v>
       </c>
       <c r="AB25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="AC25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="AD25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="AE25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
       <c r="AF25">
         <f>'Cost Components'!$N$26 * 10^6</f>
-        <v>1727761904.7619045</v>
+        <v>1816761904.7619045</v>
       </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
@@ -26372,123 +26372,123 @@
       </c>
       <c r="C26">
         <f>C25/(1+Inputs!$C$5)^'LCOF Baseline'!C$24</f>
-        <v>1614730752.1139293</v>
+        <v>1697908322.2073872</v>
       </c>
       <c r="D26">
         <f>D25/(1+Inputs!$C$5)^'LCOF Baseline'!D$24</f>
-        <v>1509094160.8541396</v>
+        <v>1586830207.6704555</v>
       </c>
       <c r="E26">
         <f>E25/(1+Inputs!$C$5)^'LCOF Baseline'!E$24</f>
-        <v>1410368374.6300368</v>
+        <v>1483018885.6733227</v>
       </c>
       <c r="F26">
         <f>F25/(1+Inputs!$C$5)^'LCOF Baseline'!F$24</f>
-        <v>1318101284.7009692</v>
+        <v>1385998958.573199</v>
       </c>
       <c r="G26">
         <f>G25/(1+Inputs!$C$5)^'LCOF Baseline'!G$24</f>
-        <v>1231870359.5336158</v>
+        <v>1295326129.5076625</v>
       </c>
       <c r="H26">
         <f>H25/(1+Inputs!$C$5)^'LCOF Baseline'!H$24</f>
-        <v>1151280709.844501</v>
+        <v>1210585167.7641706</v>
       </c>
       <c r="I26">
         <f>I25/(1+Inputs!$C$5)^'LCOF Baseline'!I$24</f>
-        <v>1309494433.4352272</v>
+        <v>1364919160.462956</v>
       </c>
       <c r="J26">
         <f>J25/(1+Inputs!$C$5)^'LCOF Baseline'!J$24</f>
-        <v>1005573159.0920613</v>
+        <v>1057371969.3983496</v>
       </c>
       <c r="K26">
         <f>K25/(1+Inputs!$C$5)^'LCOF Baseline'!K$24</f>
-        <v>939787999.15145898</v>
+        <v>988198102.24144816</v>
       </c>
       <c r="L26">
         <f>L25/(1+Inputs!$C$5)^'LCOF Baseline'!L$24</f>
-        <v>878306541.26304579</v>
+        <v>923549628.26303577</v>
       </c>
       <c r="M26">
         <f>M25/(1+Inputs!$C$5)^'LCOF Baseline'!M$24</f>
-        <v>820847234.82527637</v>
+        <v>863130493.70377159</v>
       </c>
       <c r="N26">
         <f>N25/(1+Inputs!$C$5)^'LCOF Baseline'!N$24</f>
-        <v>767146948.43483794</v>
+        <v>806664012.80726337</v>
       </c>
       <c r="O26">
         <f>O25/(1+Inputs!$C$5)^'LCOF Baseline'!O$24</f>
-        <v>872571432.85057342</v>
+        <v>909503268.7126534</v>
       </c>
       <c r="P26">
         <f>P25/(1+Inputs!$C$5)^'LCOF Baseline'!P$24</f>
-        <v>670055855.0395999</v>
+        <v>704571589.49014175</v>
       </c>
       <c r="Q26">
         <f>Q25/(1+Inputs!$C$5)^'LCOF Baseline'!Q$24</f>
-        <v>626220425.27065396</v>
+        <v>658478121.01882398</v>
       </c>
       <c r="R26">
         <f>R25/(1+Inputs!$C$5)^'LCOF Baseline'!R$24</f>
-        <v>585252733.8978076</v>
+        <v>615400113.10170472</v>
       </c>
       <c r="S26">
         <f>S25/(1+Inputs!$C$5)^'LCOF Baseline'!S$24</f>
-        <v>546965171.86710989</v>
+        <v>575140292.61841571</v>
       </c>
       <c r="T26">
         <f>T25/(1+Inputs!$C$5)^'LCOF Baseline'!T$24</f>
-        <v>511182403.61412132</v>
+        <v>537514292.16674364</v>
       </c>
       <c r="U26">
         <f>U25/(1+Inputs!$C$5)^'LCOF Baseline'!U$24</f>
-        <v>581431189.00441182</v>
+        <v>606040430.64237666</v>
       </c>
       <c r="V26">
         <f>V25/(1+Inputs!$C$5)^'LCOF Baseline'!V$24</f>
-        <v>446486508.52836174</v>
+        <v>469485799.77879608</v>
       </c>
       <c r="W26">
         <f>W25/(1+Inputs!$C$5)^'LCOF Baseline'!W$24</f>
-        <v>417277110.7741698</v>
+        <v>438771775.4942019</v>
       </c>
       <c r="X26">
         <f>X25/(1+Inputs!$C$5)^'LCOF Baseline'!X$24</f>
-        <v>389978608.20015872</v>
+        <v>410067079.90112329</v>
       </c>
       <c r="Y26">
         <f>Y25/(1+Inputs!$C$5)^'LCOF Baseline'!Y$24</f>
-        <v>364465988.97211093</v>
+        <v>383240261.58983481</v>
       </c>
       <c r="Z26">
         <f>Z25/(1+Inputs!$C$5)^'LCOF Baseline'!Z$24</f>
-        <v>340622419.60010368</v>
+        <v>358168468.77554655</v>
       </c>
       <c r="AA26">
         <f>AA25/(1+Inputs!$C$5)^'LCOF Baseline'!AA$24</f>
-        <v>387432151.47747874</v>
+        <v>403830328.27695811</v>
       </c>
       <c r="AB26">
         <f>AB25/(1+Inputs!$C$5)^'LCOF Baseline'!AB$24</f>
-        <v>297512812.99685884</v>
+        <v>312838211.87487692</v>
       </c>
       <c r="AC26">
         <f>AC25/(1+Inputs!$C$5)^'LCOF Baseline'!AC$24</f>
-        <v>278049357.94098949</v>
+        <v>292372160.63072604</v>
       </c>
       <c r="AD26">
         <f>AD25/(1+Inputs!$C$5)^'LCOF Baseline'!AD$24</f>
-        <v>259859213.02896219</v>
+        <v>273245009.93525803</v>
       </c>
       <c r="AE26">
         <f>AE25/(1+Inputs!$C$5)^'LCOF Baseline'!AE$24</f>
-        <v>242859077.59716094</v>
+        <v>255369168.16379252</v>
       </c>
       <c r="AF26">
         <f>AF25/(1+Inputs!$C$5)^'LCOF Baseline'!AF$24</f>
-        <v>226971100.55809435</v>
+        <v>238662773.98485282</v>
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
@@ -27009,7 +27009,7 @@
       </c>
       <c r="B32">
         <f>(SUM(B26:AF26) - SUM(B28:AF28)) / SUM(B30:AF30)</f>
-        <v>11.19019722051457</v>
+        <v>11.755599672709472</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.25">
@@ -27125,123 +27125,123 @@
       </c>
       <c r="C36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="D36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="E36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="F36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="G36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="H36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="I36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="J36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="K36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="L36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="M36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="N36">
         <f>'Cost Components'!$T$26 * 10^6 + 'Cost Components'!$T$7 * 10^6</f>
-        <v>962839999.99999988</v>
+        <v>1005839999.9999999</v>
       </c>
       <c r="O36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="P36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="Q36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="R36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="S36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="T36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="U36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="V36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="W36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="X36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="Y36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="Z36">
         <f>'Cost Components'!$T$26 * 10^6 + 'Cost Components'!$T$7 * 10^6</f>
-        <v>962839999.99999988</v>
+        <v>1005839999.9999999</v>
       </c>
       <c r="AA36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="AB36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="AC36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="AD36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="AE36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
       <c r="AF36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>893839999.99999988</v>
+        <v>936839999.99999988</v>
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
@@ -27254,123 +27254,123 @@
       </c>
       <c r="C37">
         <f>C36/(1+Inputs!$C$5)^'LCOF Baseline'!C$35</f>
-        <v>835364485.98130822</v>
+        <v>875551401.86915874</v>
       </c>
       <c r="D37">
         <f>D36/(1+Inputs!$C$5)^'LCOF Baseline'!D$35</f>
-        <v>780714472.87972736</v>
+        <v>818272338.19547546</v>
       </c>
       <c r="E37">
         <f>E36/(1+Inputs!$C$5)^'LCOF Baseline'!E$35</f>
-        <v>729639694.28011894</v>
+        <v>764740502.98642564</v>
       </c>
       <c r="F37">
         <f>F36/(1+Inputs!$C$5)^'LCOF Baseline'!F$35</f>
-        <v>681906256.33655989</v>
+        <v>714710750.45460343</v>
       </c>
       <c r="G37">
         <f>G36/(1+Inputs!$C$5)^'LCOF Baseline'!G$35</f>
-        <v>637295566.66968203</v>
+        <v>667953972.38747978</v>
       </c>
       <c r="H37">
         <f>H36/(1+Inputs!$C$5)^'LCOF Baseline'!H$35</f>
-        <v>595603333.33615148</v>
+        <v>624256048.96026146</v>
       </c>
       <c r="I37">
         <f>I36/(1+Inputs!$C$5)^'LCOF Baseline'!I$35</f>
-        <v>556638629.2861228</v>
+        <v>583416868.18716025</v>
       </c>
       <c r="J37">
         <f>J36/(1+Inputs!$C$5)^'LCOF Baseline'!J$35</f>
-        <v>520223018.02441388</v>
+        <v>545249409.52071059</v>
       </c>
       <c r="K37">
         <f>K36/(1+Inputs!$C$5)^'LCOF Baseline'!K$35</f>
-        <v>486189736.4714148</v>
+        <v>509578887.40253317</v>
       </c>
       <c r="L37">
         <f>L36/(1+Inputs!$C$5)^'LCOF Baseline'!L$35</f>
-        <v>454382931.28169608</v>
+        <v>476241950.84348893</v>
       </c>
       <c r="M37">
         <f>M36/(1+Inputs!$C$5)^'LCOF Baseline'!M$35</f>
-        <v>424656945.12308043</v>
+        <v>445085935.36774665</v>
       </c>
       <c r="N37">
         <f>N36/(1+Inputs!$C$5)^'LCOF Baseline'!N$35</f>
-        <v>427512474.8353495</v>
+        <v>446604989.08270115</v>
       </c>
       <c r="O37">
         <f>O36/(1+Inputs!$C$5)^'LCOF Baseline'!O$35</f>
-        <v>370911822.10069042</v>
+        <v>388755293.35989755</v>
       </c>
       <c r="P37">
         <f>P36/(1+Inputs!$C$5)^'LCOF Baseline'!P$35</f>
-        <v>346646562.71092564</v>
+        <v>363322704.07467061</v>
       </c>
       <c r="Q37">
         <f>Q36/(1+Inputs!$C$5)^'LCOF Baseline'!Q$35</f>
-        <v>323968750.19712675</v>
+        <v>339553929.04174817</v>
       </c>
       <c r="R37">
         <f>R36/(1+Inputs!$C$5)^'LCOF Baseline'!R$35</f>
-        <v>302774532.89451098</v>
+        <v>317340120.5997647</v>
       </c>
       <c r="S37">
         <f>S36/(1+Inputs!$C$5)^'LCOF Baseline'!S$35</f>
-        <v>282966853.17244017</v>
+        <v>296579551.96239692</v>
       </c>
       <c r="T37">
         <f>T36/(1+Inputs!$C$5)^'LCOF Baseline'!T$35</f>
-        <v>264455002.96489736</v>
+        <v>277177151.3667261</v>
       </c>
       <c r="U37">
         <f>U36/(1+Inputs!$C$5)^'LCOF Baseline'!U$35</f>
-        <v>247154208.37840873</v>
+        <v>259044066.69787484</v>
       </c>
       <c r="V37">
         <f>V36/(1+Inputs!$C$5)^'LCOF Baseline'!V$35</f>
-        <v>230985241.47514838</v>
+        <v>242097258.59614474</v>
       </c>
       <c r="W37">
         <f>W36/(1+Inputs!$C$5)^'LCOF Baseline'!W$35</f>
-        <v>215874057.45340967</v>
+        <v>226259120.1833128</v>
       </c>
       <c r="X37">
         <f>X36/(1+Inputs!$C$5)^'LCOF Baseline'!X$35</f>
-        <v>201751455.56393427</v>
+        <v>211457121.66664749</v>
       </c>
       <c r="Y37">
         <f>Y36/(1+Inputs!$C$5)^'LCOF Baseline'!Y$35</f>
-        <v>188552762.20928437</v>
+        <v>197623478.1931285</v>
       </c>
       <c r="Z37">
         <f>Z36/(1+Inputs!$C$5)^'LCOF Baseline'!Z$35</f>
-        <v>189820651.55149907</v>
+        <v>198297956.2092973</v>
       </c>
       <c r="AA37">
         <f>AA36/(1+Inputs!$C$5)^'LCOF Baseline'!AA$35</f>
-        <v>164689284.83647859</v>
+        <v>172611999.46993491</v>
       </c>
       <c r="AB37">
         <f>AB36/(1+Inputs!$C$5)^'LCOF Baseline'!AB$35</f>
-        <v>153915219.4733445</v>
+        <v>161319625.67283636</v>
       </c>
       <c r="AC37">
         <f>AC36/(1+Inputs!$C$5)^'LCOF Baseline'!AC$35</f>
-        <v>143845999.50779858</v>
+        <v>150766005.30171621</v>
       </c>
       <c r="AD37">
         <f>AD36/(1+Inputs!$C$5)^'LCOF Baseline'!AD$35</f>
-        <v>134435513.55869028</v>
+        <v>140902808.69319275</v>
       </c>
       <c r="AE37">
         <f>AE36/(1+Inputs!$C$5)^'LCOF Baseline'!AE$35</f>
-        <v>125640666.87728062</v>
+        <v>131684867.9375633</v>
       </c>
       <c r="AF37">
         <f>AF36/(1+Inputs!$C$5)^'LCOF Baseline'!AF$35</f>
-        <v>117421183.99745853</v>
+        <v>123069970.0351059</v>
       </c>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="B43">
         <f>(SUM(B37:AF37) - SUM(B39:AF39)) / SUM(B41:AF41)</f>
-        <v>5.3611815056150789</v>
+        <v>5.634353476900257</v>
       </c>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.25">
@@ -28007,123 +28007,123 @@
       </c>
       <c r="C47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="D47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="E47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="F47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="G47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="H47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="I47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="J47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="K47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="L47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="M47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="N47">
         <f>'Cost Components'!$Z$26* 10^6 + 'Cost Components'!$Z$7 * 10^6</f>
-        <v>937246736.84210527</v>
+        <v>980246736.84210527</v>
       </c>
       <c r="O47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="P47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="Q47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="R47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="S47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="T47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="U47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="V47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="W47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="X47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="Y47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="Z47">
         <f>'Cost Components'!$Z$26 * 10^6 + 'Cost Components'!$Z$7 * 10^6</f>
-        <v>937246736.84210527</v>
+        <v>980246736.84210527</v>
       </c>
       <c r="AA47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="AB47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="AC47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="AD47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="AE47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
       <c r="AF47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>868246736.84210527</v>
+        <v>911246736.84210527</v>
       </c>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.25">
@@ -28136,123 +28136,123 @@
       </c>
       <c r="C48">
         <f>C47/(1+Inputs!$C$5)^'LCOF Baseline'!C$46</f>
-        <v>811445548.45056558</v>
+        <v>851632464.3384161</v>
       </c>
       <c r="D48">
         <f>D47/(1+Inputs!$C$5)^'LCOF Baseline'!D$46</f>
-        <v>758360325.65473425</v>
+        <v>795918190.97048235</v>
       </c>
       <c r="E48">
         <f>E47/(1+Inputs!$C$5)^'LCOF Baseline'!E$46</f>
-        <v>708747967.90162075</v>
+        <v>743848776.60792744</v>
       </c>
       <c r="F48">
         <f>F47/(1+Inputs!$C$5)^'LCOF Baseline'!F$46</f>
-        <v>662381278.41272974</v>
+        <v>695185772.53077328</v>
       </c>
       <c r="G48">
         <f>G47/(1+Inputs!$C$5)^'LCOF Baseline'!G$46</f>
-        <v>619047923.75021458</v>
+        <v>649706329.46801233</v>
       </c>
       <c r="H48">
         <f>H47/(1+Inputs!$C$5)^'LCOF Baseline'!H$46</f>
-        <v>578549461.44879878</v>
+        <v>607202177.07290876</v>
       </c>
       <c r="I48">
         <f>I47/(1+Inputs!$C$5)^'LCOF Baseline'!I$46</f>
-        <v>540700431.26055956</v>
+        <v>567478670.16159701</v>
       </c>
       <c r="J48">
         <f>J47/(1+Inputs!$C$5)^'LCOF Baseline'!J$46</f>
-        <v>505327505.85099024</v>
+        <v>530353897.34728688</v>
       </c>
       <c r="K48">
         <f>K47/(1+Inputs!$C$5)^'LCOF Baseline'!K$46</f>
-        <v>472268697.05700016</v>
+        <v>495657847.98811853</v>
       </c>
       <c r="L48">
         <f>L47/(1+Inputs!$C$5)^'LCOF Baseline'!L$46</f>
-        <v>441372614.07196283</v>
+        <v>463231633.63375568</v>
       </c>
       <c r="M48">
         <f>M47/(1+Inputs!$C$5)^'LCOF Baseline'!M$46</f>
-        <v>412497770.16071284</v>
+        <v>432926760.40537906</v>
       </c>
       <c r="N48">
         <f>N47/(1+Inputs!$C$5)^'LCOF Baseline'!N$46</f>
-        <v>416148759.91724902</v>
+        <v>435241274.16460061</v>
       </c>
       <c r="O48">
         <f>O47/(1+Inputs!$C$5)^'LCOF Baseline'!O$46</f>
-        <v>360291527.78470862</v>
+        <v>378134999.04391575</v>
       </c>
       <c r="P48">
         <f>P47/(1+Inputs!$C$5)^'LCOF Baseline'!P$46</f>
-        <v>336721054.00440061</v>
+        <v>353397195.36814559</v>
       </c>
       <c r="Q48">
         <f>Q47/(1+Inputs!$C$5)^'LCOF Baseline'!Q$46</f>
-        <v>314692573.83588839</v>
+        <v>330277752.68050987</v>
       </c>
       <c r="R48">
         <f>R47/(1+Inputs!$C$5)^'LCOF Baseline'!R$46</f>
-        <v>294105209.19241905</v>
+        <v>308670796.89767277</v>
       </c>
       <c r="S48">
         <f>S47/(1+Inputs!$C$5)^'LCOF Baseline'!S$46</f>
-        <v>274864681.48824215</v>
+        <v>288477380.27819884</v>
       </c>
       <c r="T48">
         <f>T47/(1+Inputs!$C$5)^'LCOF Baseline'!T$46</f>
-        <v>256882879.89555338</v>
+        <v>269605028.29738212</v>
       </c>
       <c r="U48">
         <f>U47/(1+Inputs!$C$5)^'LCOF Baseline'!U$46</f>
-        <v>240077457.84631157</v>
+        <v>251967316.16577765</v>
       </c>
       <c r="V48">
         <f>V47/(1+Inputs!$C$5)^'LCOF Baseline'!V$46</f>
-        <v>224371455.93113232</v>
+        <v>235483473.05212867</v>
       </c>
       <c r="W48">
         <f>W47/(1+Inputs!$C$5)^'LCOF Baseline'!W$46</f>
-        <v>209692949.46834794</v>
+        <v>220078012.19825107</v>
       </c>
       <c r="X48">
         <f>X47/(1+Inputs!$C$5)^'LCOF Baseline'!X$46</f>
-        <v>195974719.12929714</v>
+        <v>205680385.23201036</v>
       </c>
       <c r="Y48">
         <f>Y47/(1+Inputs!$C$5)^'LCOF Baseline'!Y$46</f>
-        <v>183153943.11149266</v>
+        <v>192224659.09533679</v>
       </c>
       <c r="Z48">
         <f>Z47/(1+Inputs!$C$5)^'LCOF Baseline'!Z$46</f>
-        <v>184775026.22646007</v>
+        <v>193252330.88425833</v>
       </c>
       <c r="AA48">
         <f>AA47/(1+Inputs!$C$5)^'LCOF Baseline'!AA$46</f>
-        <v>159973747.14952627</v>
+        <v>167896461.78298259</v>
       </c>
       <c r="AB48">
         <f>AB47/(1+Inputs!$C$5)^'LCOF Baseline'!AB$46</f>
-        <v>149508174.90609935</v>
+        <v>156912581.10559121</v>
       </c>
       <c r="AC48">
         <f>AC47/(1+Inputs!$C$5)^'LCOF Baseline'!AC$46</f>
-        <v>139727266.26738253</v>
+        <v>146647272.06130016</v>
       </c>
       <c r="AD48">
         <f>AD47/(1+Inputs!$C$5)^'LCOF Baseline'!AD$46</f>
-        <v>130586230.1564323</v>
+        <v>137053525.29093477</v>
       </c>
       <c r="AE48">
         <f>AE47/(1+Inputs!$C$5)^'LCOF Baseline'!AE$46</f>
-        <v>122043205.75367504</v>
+        <v>128087406.81395772</v>
       </c>
       <c r="AF48">
         <f>AF47/(1+Inputs!$C$5)^'LCOF Baseline'!AF$46</f>
-        <v>114059070.79782715</v>
+        <v>119707856.83547451</v>
       </c>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.25">
@@ -28773,7 +28773,7 @@
       </c>
       <c r="B54">
         <f>(SUM(B48:AF48) - SUM(B50:AF50)) / SUM(B52:AF52)</f>
-        <v>5.1985916882089755</v>
+        <v>5.4717636594941528</v>
       </c>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.25">
@@ -28889,123 +28889,123 @@
       </c>
       <c r="C58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="D58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="E58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="F58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="G58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="H58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="I58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="J58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="K58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="L58">
         <f>'Cost Components'!$AF$26*10^6 + 'Cost Components'!$AF$7 * 10^6</f>
-        <v>889404631.57894742</v>
+        <v>932404631.57894742</v>
       </c>
       <c r="M58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="N58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="O58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="P58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="Q58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="R58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="S58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="T58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="U58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="V58">
         <f>'Cost Components'!$AF$26*10^6 + 'Cost Components'!$AF$7 * 10^6</f>
-        <v>889404631.57894742</v>
+        <v>932404631.57894742</v>
       </c>
       <c r="W58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="X58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="Y58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="Z58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AA58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AB58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AC58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AD58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AE58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
       <c r="AF58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>819404631.57894742</v>
+        <v>862404631.57894742</v>
       </c>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.25">
@@ -29018,123 +29018,123 @@
       </c>
       <c r="C59">
         <f>C58/(1+Inputs!$C$5)^'LCOF Baseline'!C$57</f>
-        <v>765798721.10181999</v>
+        <v>805985636.9896704</v>
       </c>
       <c r="D59">
         <f>D58/(1+Inputs!$C$5)^'LCOF Baseline'!D$57</f>
-        <v>715699739.34749532</v>
+        <v>753257604.66324341</v>
       </c>
       <c r="E59">
         <f>E58/(1+Inputs!$C$5)^'LCOF Baseline'!E$57</f>
-        <v>668878261.07242548</v>
+        <v>703979069.77873218</v>
       </c>
       <c r="F59">
         <f>F58/(1+Inputs!$C$5)^'LCOF Baseline'!F$57</f>
-        <v>625119870.16114533</v>
+        <v>657924364.27918899</v>
       </c>
       <c r="G59">
         <f>G58/(1+Inputs!$C$5)^'LCOF Baseline'!G$57</f>
-        <v>584224177.72069657</v>
+        <v>614882583.43849432</v>
       </c>
       <c r="H59">
         <f>H58/(1+Inputs!$C$5)^'LCOF Baseline'!H$57</f>
-        <v>546003904.41186595</v>
+        <v>574656620.03597605</v>
       </c>
       <c r="I59">
         <f>I58/(1+Inputs!$C$5)^'LCOF Baseline'!I$57</f>
-        <v>510284022.81482798</v>
+        <v>537062261.71586537</v>
       </c>
       <c r="J59">
         <f>J58/(1+Inputs!$C$5)^'LCOF Baseline'!J$57</f>
-        <v>476900955.90170842</v>
+        <v>501927347.39800507</v>
       </c>
       <c r="K59">
         <f>K58/(1+Inputs!$C$5)^'LCOF Baseline'!K$57</f>
-        <v>445701827.94552183</v>
+        <v>469090978.8766402</v>
       </c>
       <c r="L59">
         <f>L58/(1+Inputs!$C$5)^'LCOF Baseline'!L$57</f>
-        <v>452128214.8844974</v>
+        <v>473987234.44629025</v>
       </c>
       <c r="M59">
         <f>M58/(1+Inputs!$C$5)^'LCOF Baseline'!M$57</f>
-        <v>389293237.78978235</v>
+        <v>409722228.03444856</v>
       </c>
       <c r="N59">
         <f>N58/(1+Inputs!$C$5)^'LCOF Baseline'!N$57</f>
-        <v>363825455.87830132</v>
+        <v>382917970.12565291</v>
       </c>
       <c r="O59">
         <f>O58/(1+Inputs!$C$5)^'LCOF Baseline'!O$57</f>
-        <v>340023790.54046851</v>
+        <v>357867261.79967558</v>
       </c>
       <c r="P59">
         <f>P58/(1+Inputs!$C$5)^'LCOF Baseline'!P$57</f>
-        <v>317779243.49576497</v>
+        <v>334455384.85950994</v>
       </c>
       <c r="Q59">
         <f>Q58/(1+Inputs!$C$5)^'LCOF Baseline'!Q$57</f>
-        <v>296989947.19230366</v>
+        <v>312575126.03692514</v>
       </c>
       <c r="R59">
         <f>R58/(1+Inputs!$C$5)^'LCOF Baseline'!R$57</f>
-        <v>277560698.31056422</v>
+        <v>292126286.01581794</v>
       </c>
       <c r="S59">
         <f>S58/(1+Inputs!$C$5)^'LCOF Baseline'!S$57</f>
-        <v>259402521.78557402</v>
+        <v>273015220.57553077</v>
       </c>
       <c r="T59">
         <f>T58/(1+Inputs!$C$5)^'LCOF Baseline'!T$57</f>
-        <v>242432263.35100377</v>
+        <v>255154411.75283247</v>
       </c>
       <c r="U59">
         <f>U58/(1+Inputs!$C$5)^'LCOF Baseline'!U$57</f>
-        <v>226572208.73925585</v>
+        <v>238462067.05872193</v>
       </c>
       <c r="V59">
         <f>V58/(1+Inputs!$C$5)^'LCOF Baseline'!V$57</f>
-        <v>229839057.99066788</v>
+        <v>240951075.11166424</v>
       </c>
       <c r="W59">
         <f>W58/(1+Inputs!$C$5)^'LCOF Baseline'!W$57</f>
-        <v>197896941.86326826</v>
+        <v>208282004.59317139</v>
       </c>
       <c r="X59">
         <f>X58/(1+Inputs!$C$5)^'LCOF Baseline'!X$57</f>
-        <v>184950412.9563255</v>
+        <v>194656079.0590387</v>
       </c>
       <c r="Y59">
         <f>Y58/(1+Inputs!$C$5)^'LCOF Baseline'!Y$57</f>
-        <v>172850853.23021072</v>
+        <v>181921569.21405485</v>
       </c>
       <c r="Z59">
         <f>Z58/(1+Inputs!$C$5)^'LCOF Baseline'!Z$57</f>
-        <v>161542853.48617825</v>
+        <v>170020158.14397648</v>
       </c>
       <c r="AA59">
         <f>AA58/(1+Inputs!$C$5)^'LCOF Baseline'!AA$57</f>
-        <v>150974629.4263348</v>
+        <v>158897344.05979109</v>
       </c>
       <c r="AB59">
         <f>AB58/(1+Inputs!$C$5)^'LCOF Baseline'!AB$57</f>
-        <v>141097784.5105933</v>
+        <v>148502190.71008515</v>
       </c>
       <c r="AC59">
         <f>AC58/(1+Inputs!$C$5)^'LCOF Baseline'!AC$57</f>
-        <v>131867088.32765725</v>
+        <v>138787094.12157488</v>
       </c>
       <c r="AD59">
         <f>AD58/(1+Inputs!$C$5)^'LCOF Baseline'!AD$57</f>
-        <v>123240269.46510026</v>
+        <v>129707564.59960271</v>
       </c>
       <c r="AE59">
         <f>AE58/(1+Inputs!$C$5)^'LCOF Baseline'!AE$57</f>
-        <v>115177821.93000023</v>
+        <v>121222022.99028291</v>
       </c>
       <c r="AF59">
         <f>AF58/(1+Inputs!$C$5)^'LCOF Baseline'!AF$57</f>
-        <v>107642824.23364508</v>
+        <v>113291610.27129245</v>
       </c>
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.25">
@@ -29655,7 +29655,7 @@
       </c>
       <c r="B65">
         <f>(SUM(B59:AF59) - SUM(B61:AF61)) / SUM(B63:AF63)</f>
-        <v>4.8649780783648957</v>
+        <v>5.1381500496500747</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Peacock_2024_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Peacock_2024_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{EB5A70C5-0542-CC4D-B2C3-B66A3176FC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8978432-6DE3-459E-8395-F72F9F10AC4E}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="1" r:id="rId1"/>
@@ -965,7 +965,7 @@
         </row>
         <row r="34">
           <cell r="C34">
-            <v>523</v>
+            <v>497</v>
           </cell>
         </row>
       </sheetData>
@@ -1313,14 +1313,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1406,12 +1406,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C47D2BC9-8FE5-1449-9DFF-90664D21177E}">
   <dimension ref="A1:AF24"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1509,12 +1509,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>161</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>180104317.61894262</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>53732114.084283352</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>120</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -1997,12 +1997,12 @@
         <v>23711764.646403477</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>161</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>0.66905215553408037</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>0.19960424727603457</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>4.3259050090031316E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>162</v>
       </c>
@@ -2038,12 +2038,12 @@
         <v>8.8084547099855262E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -2052,126 +2052,126 @@
       </c>
       <c r="C15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!C1</f>
-        <v>488785046.72897196</v>
+        <v>464485981.30841118</v>
       </c>
       <c r="D15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!D1</f>
-        <v>456808454.8868897</v>
+        <v>434099047.95178616</v>
       </c>
       <c r="E15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!E1</f>
-        <v>426923789.61391556</v>
+        <v>405700044.81475341</v>
       </c>
       <c r="F15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!F1</f>
-        <v>398994195.90085572</v>
+        <v>379158920.38762003</v>
       </c>
       <c r="G15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!G1</f>
-        <v>372891771.86995852</v>
+        <v>354354131.20338315</v>
       </c>
       <c r="H15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!H1</f>
-        <v>348496983.05603606</v>
+        <v>331172085.23680675</v>
       </c>
       <c r="I15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!I1</f>
-        <v>325698115.00564116</v>
+        <v>309506621.71664178</v>
       </c>
       <c r="J15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!J1</f>
-        <v>304390761.68751508</v>
+        <v>289258524.96882409</v>
       </c>
       <c r="K15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!K1</f>
-        <v>284477347.37150943</v>
+        <v>270335070.06432158</v>
       </c>
       <c r="L15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!L1</f>
-        <v>265866679.78645742</v>
+        <v>252649598.19095474</v>
       </c>
       <c r="M15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!M1</f>
-        <v>248473532.51070783</v>
+        <v>236121119.80463058</v>
       </c>
       <c r="N15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!N1</f>
-        <v>232218254.68290454</v>
+        <v>220673943.74264544</v>
       </c>
       <c r="O15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!O1</f>
-        <v>217026406.24570519</v>
+        <v>206237330.60060319</v>
       </c>
       <c r="P15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!P1</f>
-        <v>202828417.05206093</v>
+        <v>192745168.78561047</v>
       </c>
       <c r="Q15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!Q1</f>
-        <v>189559268.27295411</v>
+        <v>180135671.76225275</v>
       </c>
       <c r="R15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!R1</f>
-        <v>177158194.64762068</v>
+        <v>168351095.10490915</v>
       </c>
       <c r="S15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!S1</f>
-        <v>165568406.2127296</v>
+        <v>157337472.06066275</v>
       </c>
       <c r="T15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!T1</f>
-        <v>154736828.23619589</v>
+        <v>147044366.41183433</v>
       </c>
       <c r="U15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!U1</f>
-        <v>144613858.16466907</v>
+        <v>137424641.50638723</v>
       </c>
       <c r="V15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!V1</f>
-        <v>135153138.47165334</v>
+        <v>128434244.39849274</v>
       </c>
       <c r="W15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!W1</f>
-        <v>126311344.36603114</v>
+        <v>120032004.11074087</v>
       </c>
       <c r="X15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!X1</f>
-        <v>118047985.38881415</v>
+        <v>112179443.09415035</v>
       </c>
       <c r="Y15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!Y1</f>
-        <v>110325219.98954594</v>
+        <v>104840601.02257042</v>
       </c>
       <c r="Z15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!Z1</f>
-        <v>103107682.2332205</v>
+        <v>97981870.114551798</v>
       </c>
       <c r="AA15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AA1</f>
-        <v>96362319.844131306</v>
+        <v>91571841.228553072</v>
       </c>
       <c r="AB15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AB1</f>
-        <v>90058242.844982535</v>
+        <v>85581160.026685119</v>
       </c>
       <c r="AC15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AC1</f>
-        <v>84166582.098114491</v>
+        <v>79982392.548303828</v>
       </c>
       <c r="AD15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AD1</f>
-        <v>78660357.1010416</v>
+        <v>74749899.577854067</v>
       </c>
       <c r="AE15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AE1</f>
-        <v>73514352.430879995</v>
+        <v>69859719.231639311</v>
       </c>
       <c r="AF15">
         <f>('Cost Components'!$Z$24 * 10^6) / (1+Inputs!$C$5) ^ 'Cost Breakdowns'!AF1</f>
-        <v>68705002.271850467</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+        <v>65289457.225831136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>39179814.019710958</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>120</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>162</v>
       </c>
@@ -2526,45 +2526,45 @@
         <v>18522763.518797163</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>161</v>
       </c>
       <c r="B21" s="16">
         <f>SUM(B15:AF15) / SUM($B$15:$AF$18)</f>
-        <v>0.50739989886540982</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+        <v>0.49465278359016118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="16">
         <f t="shared" ref="B22:B24" si="1">SUM(B16:AF16) / SUM($B$15:$AF$18)</f>
-        <v>0.28935060059392492</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+        <v>0.29683818626887254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>120</v>
       </c>
       <c r="B23" s="16">
         <f t="shared" si="1"/>
-        <v>6.6455263944063481E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+        <v>6.8174940631483771E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>162</v>
       </c>
       <c r="B24" s="16">
         <f t="shared" si="1"/>
-        <v>0.13679423659660192</v>
+        <v>0.14033408950948237</v>
       </c>
     </row>
   </sheetData>
@@ -2575,29 +2575,29 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:T36"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.19921875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.69921875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.19921875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.69921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>165</v>
       </c>
@@ -2623,7 +2623,7 @@
       <c r="S1" s="30"/>
       <c r="T1" s="30"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>20</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>172</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>11.755599672709472</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>172</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>13.061777414121636</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>174</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>175</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>6.2090000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>177</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>88.7</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>178</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>82.491</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>178</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>2861.5797936000004</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>180</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>4284.9678494185027</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="29" t="s">
         <v>181</v>
       </c>
@@ -3249,7 +3249,7 @@
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>20</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>172</v>
       </c>
@@ -3322,11 +3322,11 @@
       </c>
       <c r="E15" s="14">
         <f>'LCOF CO2 Cost Corrected'!B43</f>
-        <v>5.677808394564976</v>
+        <v>5.5126346444855638</v>
       </c>
       <c r="F15" s="14">
         <f>'LCOF WACC Corrected '!B43</f>
-        <v>5.634353476900257</v>
+        <v>5.4691797268208457</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>172</v>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="L15" s="14">
         <f>'LCOF CO2 Cost Corrected'!B54</f>
-        <v>5.5152185771588691</v>
+        <v>5.3500448270794587</v>
       </c>
       <c r="M15" s="14">
         <f>'LCOF WACC Corrected '!B54</f>
-        <v>5.4717636594941528</v>
+        <v>5.3065899094147477</v>
       </c>
       <c r="O15" s="11" t="s">
         <v>172</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="S15" s="14">
         <f>'LCOF CO2 Cost Corrected'!B65</f>
-        <v>5.179064767127346</v>
+        <v>5.0138910170479321</v>
       </c>
       <c r="T15" s="14">
         <f>'LCOF WACC Corrected '!B65</f>
-        <v>5.1381500496500747</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+        <v>4.9729762995706661</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>172</v>
       </c>
@@ -3390,11 +3390,11 @@
       </c>
       <c r="E16" s="14">
         <f>E15/Inputs!$C$6</f>
-        <v>6.3086759939610841</v>
+        <v>6.1251496049839593</v>
       </c>
       <c r="F16" s="14">
         <f>F15/Inputs!$C$6</f>
-        <v>6.2603927521113967</v>
+        <v>6.0768663631342728</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>172</v>
@@ -3412,11 +3412,11 @@
       </c>
       <c r="L16" s="14">
         <f>L15/Inputs!$C$6</f>
-        <v>6.1280206412876321</v>
+        <v>5.94449425231051</v>
       </c>
       <c r="M16" s="14">
         <f>M15/Inputs!$C$6</f>
-        <v>6.0797373994379473</v>
+        <v>5.8962110104608305</v>
       </c>
       <c r="O16" s="11" t="s">
         <v>172</v>
@@ -3434,14 +3434,14 @@
       </c>
       <c r="S16" s="14">
         <f>S15/Inputs!$C$6</f>
-        <v>5.7545164079192732</v>
+        <v>5.5709900189421466</v>
       </c>
       <c r="T16" s="14">
         <f>T15/Inputs!$C$6</f>
-        <v>5.7090556107223049</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+        <v>5.5255292217451846</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>174</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>175</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>6.2090000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>177</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>88.7</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>178</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>82.491</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>178</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>2861.5797936000004</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>180</v>
       </c>
@@ -3798,11 +3798,11 @@
       </c>
       <c r="E22" s="14">
         <f>(E16-E17) / E21 * 10^6</f>
-        <v>1610.5355525184063</v>
+        <v>1546.4009128387488</v>
       </c>
       <c r="F22" s="14">
         <f>(F16-F17) / F21 * 10^6</f>
-        <v>1593.662620315826</v>
+        <v>1529.5279806361686</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>180</v>
@@ -3820,11 +3820,11 @@
       </c>
       <c r="L22" s="14">
         <f>(L16-L17) / L21 * 10^6</f>
-        <v>1547.4042174853969</v>
+        <v>1483.2695778057403</v>
       </c>
       <c r="M22" s="14">
         <f>(M16-M17) / M21 * 10^6</f>
-        <v>1530.5312852828172</v>
+        <v>1466.3966456031624</v>
       </c>
       <c r="O22" s="11" t="s">
         <v>180</v>
@@ -3842,14 +3842,14 @@
       </c>
       <c r="S22" s="14">
         <f>(S16-S17) / S21 * 10^6</f>
-        <v>1416.8804298196776</v>
+        <v>1352.7457901400194</v>
       </c>
       <c r="T22" s="14">
         <f>(T16-T17) / T21 * 10^6</f>
-        <v>1400.9938215557243</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1336.8591818760681</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="28" t="s">
         <v>184</v>
       </c>
@@ -3866,7 +3866,7 @@
       <c r="P24" s="28"/>
       <c r="Q24" s="28"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>20</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
         <v>187</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>215.38772640000005</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>188</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>0.29529657289440003</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>189</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>13.357073987016037</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
         <v>190</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>4073.6498115786935</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="28" t="s">
         <v>191</v>
       </c>
@@ -4040,7 +4040,7 @@
       <c r="P31" s="28"/>
       <c r="Q31" s="28"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
         <v>20</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>187</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>215.38772640000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
         <v>188</v>
       </c>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="C34" s="19">
         <f>C33*Inputs!$C$33 * 10^-6</f>
-        <v>0.11264778090720001</v>
+        <v>0.10704770002080002</v>
       </c>
       <c r="H34" s="18" t="s">
         <v>188</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="J34" s="19">
         <f>J33*Inputs!$C$33 * 10^-6</f>
-        <v>0.11264778090720001</v>
+        <v>0.10704770002080002</v>
       </c>
       <c r="O34" s="18" t="s">
         <v>188</v>
@@ -4130,10 +4130,10 @@
       </c>
       <c r="Q34" s="19">
         <f>Q33*Inputs!$C$33 * 10^-6</f>
-        <v>0.11264778090720001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.10704770002080002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
         <v>189</v>
       </c>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C35" s="19">
         <f>F16+C34</f>
-        <v>6.3730405330185969</v>
+        <v>6.1839140631550729</v>
       </c>
       <c r="H35" s="18" t="s">
         <v>189</v>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="J35" s="19">
         <f>M16+J34</f>
-        <v>6.1923851803451475</v>
+        <v>6.0032587104816306</v>
       </c>
       <c r="O35" s="18" t="s">
         <v>189</v>
@@ -4162,10 +4162,10 @@
       </c>
       <c r="Q35" s="19">
         <f>T16+Q34</f>
-        <v>5.8217033916295051</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5.6325769217659847</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
         <v>190</v>
       </c>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C36" s="5">
         <f>(C35-C17) /C21 * 10^6</f>
-        <v>1633.0282117136753</v>
+        <v>1566.9365827867061</v>
       </c>
       <c r="H36" s="18" t="s">
         <v>190</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="J36" s="5">
         <f>(J35-J17) /J21 * 10^6</f>
-        <v>1569.8968766806668</v>
+        <v>1503.8052477537001</v>
       </c>
       <c r="O36" s="18" t="s">
         <v>190</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Q36" s="5">
         <f>(Q35-Q17) /Q21 * 10^6</f>
-        <v>1440.3594129535736</v>
+        <v>1374.2677840266058</v>
       </c>
     </row>
   </sheetData>
@@ -4219,14 +4219,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -4240,12 +4240,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -4280,12 +4280,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>30</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>30</v>
       </c>
@@ -4315,12 +4315,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -4401,12 +4401,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>40</v>
       </c>
@@ -4421,12 +4421,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -4456,12 +4456,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -4491,12 +4491,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -4526,12 +4526,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -4561,12 +4561,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>48</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>48</v>
       </c>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="C33" s="5">
         <f>[1]Inputs!C34</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="D33" t="s">
         <v>49</v>
@@ -4604,23 +4604,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G81"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.69921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="27.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>56</v>
       </c>
@@ -4665,12 +4665,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>64</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>5.0822692332126298</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -4849,7 +4849,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>71</v>
       </c>
@@ -4900,18 +4900,18 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B20" s="8"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B21" s="8"/>
     </row>
-    <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>78</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>80</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>81</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -5056,7 +5056,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>82</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>84</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -5114,7 +5114,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -5144,15 +5144,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B39" s="8"/>
     </row>
-    <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>91</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>92</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>93</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>95</v>
       </c>
@@ -5305,7 +5305,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>95</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>96</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>96</v>
       </c>
@@ -5353,7 +5353,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>97</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>97</v>
       </c>
@@ -5381,7 +5381,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>98</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>98</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>100</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>100</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>101</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>101</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>102</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>102</v>
       </c>
@@ -5517,12 +5517,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="65" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>20</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>33</v>
       </c>
@@ -5563,12 +5563,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>20</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="23" t="s">
         <v>107</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="22"/>
       <c r="B71">
         <v>2050</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G71" s="22"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="22"/>
       <c r="B72">
         <v>2024</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="G72" s="22"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="22"/>
       <c r="B73">
         <v>2050</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G73" s="22"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="22"/>
       <c r="B74">
         <v>2024</v>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="G74" s="22"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="22"/>
       <c r="B75">
         <v>2050</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="G75" s="22"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
         <v>109</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="22"/>
       <c r="B77">
         <v>2050</v>
@@ -5731,7 +5731,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="22"/>
       <c r="B78">
         <v>2024</v>
@@ -5747,7 +5747,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="22"/>
       <c r="B79">
         <v>2050</v>
@@ -5763,7 +5763,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="22"/>
       <c r="B80">
         <v>2024</v>
@@ -5779,7 +5779,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="22"/>
       <c r="B81">
         <v>2050</v>
@@ -5808,12 +5808,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52ECC0E-99DC-B545-8492-9611BCF80569}">
   <dimension ref="A1:AF14"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -5911,12 +5911,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>110</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -6143,12 +6143,12 @@
         <v>52.073722256095841</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2050</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>110</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>111</v>
       </c>
@@ -6375,12 +6375,12 @@
         <v>19.875466509960244</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2024</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>112</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>99377.332549801227</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -6654,15 +6654,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AI26"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>114</v>
       </c>
@@ -6706,7 +6706,7 @@
       <c r="AH1" s="25"/>
       <c r="AI1" s="26"/>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>120</v>
       </c>
@@ -6750,7 +6750,7 @@
       <c r="AH2" s="25"/>
       <c r="AI2" s="26"/>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>121</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>122</v>
       </c>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="AI4" s="9"/>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>126</v>
       </c>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="AI5" s="9"/>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>127</v>
       </c>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AI6" s="9"/>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>128</v>
       </c>
@@ -7166,7 +7166,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>132</v>
       </c>
@@ -7240,7 +7240,7 @@
       <c r="AH8" s="12"/>
       <c r="AI8" s="12"/>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
         <v>133</v>
       </c>
@@ -7284,7 +7284,7 @@
       <c r="AH10" s="25"/>
       <c r="AI10" s="26"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>121</v>
       </c>
@@ -7376,7 +7376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="AI12" s="9"/>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>136</v>
       </c>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="AI13" s="9"/>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>137</v>
       </c>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AI14" s="9"/>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>138</v>
       </c>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AI15" s="9"/>
     </row>
-    <row r="16" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>139</v>
       </c>
@@ -7758,7 +7758,7 @@
       <c r="AH16" s="12"/>
       <c r="AI16" s="12"/>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
         <v>140</v>
       </c>
@@ -7802,7 +7802,7 @@
       <c r="AH18" s="25"/>
       <c r="AI18" s="26"/>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
         <v>133</v>
       </c>
@@ -7846,7 +7846,7 @@
       <c r="AH19" s="25"/>
       <c r="AI19" s="26"/>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>121</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>146</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="22" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>148</v>
       </c>
@@ -8082,7 +8082,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>149</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>151</v>
       </c>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T24" s="14">
         <f>(Inputs!$C$33*'Study Parameters'!$C$10*10^6) / 10^6</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="U24" s="9" t="s">
         <v>134</v>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="Z24" s="14">
         <f>(Inputs!$C$33*'Study Parameters'!$C$10*10^6) / 10^6</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="AA24" s="9" t="s">
         <v>134</v>
@@ -8220,13 +8220,13 @@
       </c>
       <c r="AF24" s="14">
         <f>(Inputs!$C$33*'Study Parameters'!$C$10*10^6) / 10^6</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="AG24" s="9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>146</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="26" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>153</v>
       </c>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="T26" s="15">
         <f>T16-T12 - T13 - T14+T25+T24</f>
-        <v>936.83999999999992</v>
+        <v>910.83999999999992</v>
       </c>
       <c r="U26" s="12" t="s">
         <v>134</v>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="Z26" s="15">
         <f>Z16-Z12 - Z13 - Z14+Z25+Z24</f>
-        <v>911.24673684210529</v>
+        <v>885.24673684210529</v>
       </c>
       <c r="AA26" s="12" t="s">
         <v>134</v>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="AF26" s="15">
         <f>AF16-AF12 - AF13 - AF14+AF25+AF24</f>
-        <v>862.40463157894737</v>
+        <v>836.40463157894737</v>
       </c>
       <c r="AG26" s="12" t="s">
         <v>134</v>
@@ -8428,20 +8428,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AF65"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -8539,7 +8539,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>110</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>880500000.00000012</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>87501741.310099989</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>155</v>
       </c>
@@ -8925,7 +8925,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>156</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>157</v>
       </c>
@@ -9181,7 +9181,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>158</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -9318,12 +9318,12 @@
         <v>9.1316404015676635</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -9421,7 +9421,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>110</v>
       </c>
@@ -9550,7 +9550,7 @@
         <v>690500000.00000012</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>111</v>
       </c>
@@ -9679,7 +9679,7 @@
         <v>68620048.125637755</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>155</v>
       </c>
@@ -9807,7 +9807,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>156</v>
       </c>
@@ -9935,7 +9935,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>157</v>
       </c>
@@ -10063,7 +10063,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>158</v>
       </c>
@@ -10191,7 +10191,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>159</v>
       </c>
@@ -10200,12 +10200,12 @@
         <v>7.9246014586796623</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>110</v>
       </c>
@@ -10432,7 +10432,7 @@
         <v>585800000</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>111</v>
       </c>
@@ -10561,7 +10561,7 @@
         <v>58215241.40767356</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>155</v>
       </c>
@@ -10689,7 +10689,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>156</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>157</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>158</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>159</v>
       </c>
@@ -11082,12 +11082,12 @@
         <v>7.6253466052205301</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -11185,7 +11185,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>110</v>
       </c>
@@ -11314,7 +11314,7 @@
         <v>393000000</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -11443,7 +11443,7 @@
         <v>39055291.692071885</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>155</v>
       </c>
@@ -11571,7 +11571,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>156</v>
       </c>
@@ -11699,7 +11699,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>157</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>158</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>159</v>
       </c>
@@ -11964,12 +11964,12 @@
         <v>3.6063103110725292</v>
       </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -12067,7 +12067,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>110</v>
       </c>
@@ -12196,7 +12196,7 @@
         <v>325000000</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>111</v>
       </c>
@@ -12325,7 +12325,7 @@
         <v>32297633.078685399</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>155</v>
       </c>
@@ -12453,7 +12453,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>156</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>158</v>
       </c>
@@ -12837,7 +12837,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>159</v>
       </c>
@@ -12846,12 +12846,12 @@
         <v>3.1743174262494587</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>21</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -13078,7 +13078,7 @@
         <v>278000000</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -13207,7 +13207,7 @@
         <v>27626898.448844742</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>155</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>156</v>
       </c>
@@ -13463,7 +13463,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>157</v>
       </c>
@@ -13591,7 +13591,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>158</v>
       </c>
@@ -13719,7 +13719,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>159</v>
       </c>
@@ -13736,20 +13736,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AF65"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -13847,7 +13847,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>110</v>
       </c>
@@ -13976,7 +13976,7 @@
         <v>880500000.00000012</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -14105,7 +14105,7 @@
         <v>87501741.310099989</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>155</v>
       </c>
@@ -14233,7 +14233,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>156</v>
       </c>
@@ -14361,7 +14361,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>157</v>
       </c>
@@ -14489,7 +14489,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>158</v>
       </c>
@@ -14617,7 +14617,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -14626,12 +14626,12 @@
         <v>7.3568211313547511</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -14729,7 +14729,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>110</v>
       </c>
@@ -14858,7 +14858,7 @@
         <v>589522556.39097762</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>111</v>
       </c>
@@ -14987,7 +14987,7 @@
         <v>58585179.132075131</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>155</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>156</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>157</v>
       </c>
@@ -15371,7 +15371,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>158</v>
       </c>
@@ -15499,7 +15499,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>159</v>
       </c>
@@ -15508,12 +15508,12 @@
         <v>7.2831082650514132</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -15611,7 +15611,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>110</v>
       </c>
@@ -15740,7 +15740,7 @@
         <v>510561904.76190472</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>111</v>
       </c>
@@ -15869,7 +15869,7 @@
         <v>50738280.196783751</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>155</v>
       </c>
@@ -15997,7 +15997,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>156</v>
       </c>
@@ -16125,7 +16125,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>157</v>
       </c>
@@ -16253,7 +16253,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>158</v>
       </c>
@@ -16381,7 +16381,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>159</v>
       </c>
@@ -16390,12 +16390,12 @@
         <v>7.1473712844779129</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -16493,7 +16493,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>110</v>
       </c>
@@ -16622,7 +16622,7 @@
         <v>195660000</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -16751,7 +16751,7 @@
         <v>19444168.886694107</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>155</v>
       </c>
@@ -16879,7 +16879,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>156</v>
       </c>
@@ -17007,7 +17007,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>157</v>
       </c>
@@ -17135,7 +17135,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>158</v>
       </c>
@@ -17263,7 +17263,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>159</v>
       </c>
@@ -17272,12 +17272,12 @@
         <v>2.3526415479698048</v>
       </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -17375,7 +17375,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>110</v>
       </c>
@@ -17504,7 +17504,7 @@
         <v>194263157.89473686</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>111</v>
       </c>
@@ -17633,7 +17633,7 @@
         <v>19305354.444279809</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>155</v>
       </c>
@@ -17761,7 +17761,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>156</v>
       </c>
@@ -17889,7 +17889,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>158</v>
       </c>
@@ -18145,7 +18145,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>159</v>
       </c>
@@ -18154,12 +18154,12 @@
         <v>2.3437676384007613</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>21</v>
       </c>
@@ -18257,7 +18257,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -18386,7 +18386,7 @@
         <v>167868421.05263159</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -18515,7 +18515,7 @@
         <v>16682315.903557424</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>155</v>
       </c>
@@ -18643,7 +18643,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>156</v>
       </c>
@@ -18771,7 +18771,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>157</v>
       </c>
@@ -18899,7 +18899,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>158</v>
       </c>
@@ -19027,7 +19027,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>159</v>
       </c>
@@ -19044,23 +19044,23 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AF65"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>110</v>
       </c>
@@ -19287,7 +19287,7 @@
         <v>1856261016.9491527</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -19416,7 +19416,7 @@
         <v>184470268.38058817</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>155</v>
       </c>
@@ -19544,7 +19544,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>156</v>
       </c>
@@ -19672,7 +19672,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>157</v>
       </c>
@@ -19800,7 +19800,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>158</v>
       </c>
@@ -19928,7 +19928,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -19937,12 +19937,12 @@
         <v>11.705907867765633</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -20040,7 +20040,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>110</v>
       </c>
@@ -20169,7 +20169,7 @@
         <v>1901622556.3909774</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>111</v>
       </c>
@@ -20298,7 +20298,7 @@
         <v>188978177.17066929</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>155</v>
       </c>
@@ -20426,7 +20426,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>156</v>
       </c>
@@ -20554,7 +20554,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>157</v>
       </c>
@@ -20682,7 +20682,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>158</v>
       </c>
@@ -20810,7 +20810,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>159</v>
       </c>
@@ -20819,12 +20819,12 @@
         <v>11.994082313111065</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -20922,7 +20922,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>110</v>
       </c>
@@ -21051,7 +21051,7 @@
         <v>1816761904.7619045</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>111</v>
       </c>
@@ -21180,7 +21180,7 @@
         <v>180544951.97333407</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>155</v>
       </c>
@@ -21308,7 +21308,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>156</v>
       </c>
@@ -21436,7 +21436,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>157</v>
       </c>
@@ -21564,7 +21564,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>158</v>
       </c>
@@ -21692,7 +21692,7 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>159</v>
       </c>
@@ -21701,12 +21701,12 @@
         <v>11.820863596942624</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -21804,7 +21804,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>110</v>
       </c>
@@ -21814,126 +21814,126 @@
       </c>
       <c r="C36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="D36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="E36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="F36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="G36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="H36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="I36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="J36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="K36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="L36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="M36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="N36">
         <f>'Cost Components'!$T$26 * 10^6 + 'Cost Components'!$T$7 * 10^6</f>
-        <v>1005839999.9999999</v>
+        <v>979839999.99999988</v>
       </c>
       <c r="O36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="P36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="Q36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="R36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="S36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="T36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="U36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="V36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="W36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="X36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="Y36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="Z36">
         <f>'Cost Components'!$T$26 * 10^6 + 'Cost Components'!$T$7 * 10^6</f>
-        <v>1005839999.9999999</v>
+        <v>979839999.99999988</v>
       </c>
       <c r="AA36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="AB36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="AC36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="AD36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="AE36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="AF36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
-      </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+        <v>910839999.99999988</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -21943,126 +21943,126 @@
       </c>
       <c r="C37">
         <f>C36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!C$35</f>
-        <v>867444444.4444443</v>
+        <v>843370370.37037015</v>
       </c>
       <c r="D37">
         <f>D36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!D$35</f>
-        <v>803189300.41152251</v>
+        <v>780898491.0836761</v>
       </c>
       <c r="E37">
         <f>E36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!E$35</f>
-        <v>743693796.67733562</v>
+        <v>723054158.41081119</v>
       </c>
       <c r="F37">
         <f>F36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!F$35</f>
-        <v>688605367.2938292</v>
+        <v>669494591.12112141</v>
       </c>
       <c r="G37">
         <f>G36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!G$35</f>
-        <v>637597562.3091011</v>
+        <v>619902399.18622351</v>
       </c>
       <c r="H37">
         <f>H36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!H$35</f>
-        <v>590368113.24916756</v>
+        <v>573983702.95020688</v>
       </c>
       <c r="I37">
         <f>I36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!I$35</f>
-        <v>546637141.89737737</v>
+        <v>531466391.6205619</v>
       </c>
       <c r="J37">
         <f>J36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!J$35</f>
-        <v>506145501.75683093</v>
+        <v>492098510.75977957</v>
       </c>
       <c r="K37">
         <f>K36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!K$35</f>
-        <v>468653242.36743599</v>
+        <v>455646769.22201806</v>
       </c>
       <c r="L37">
         <f>L36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!L$35</f>
-        <v>433938187.37725556</v>
+        <v>421895156.68705374</v>
       </c>
       <c r="M37">
         <f>M36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!M$35</f>
-        <v>401794617.94190329</v>
+        <v>390643663.59912384</v>
       </c>
       <c r="N37">
         <f>N36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!N$35</f>
-        <v>399432902.9964838</v>
+        <v>389107945.27168804</v>
       </c>
       <c r="O37">
         <f>O36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!O$35</f>
-        <v>344474123.74991703</v>
+        <v>334913977.70843947</v>
       </c>
       <c r="P37">
         <f>P36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!P$35</f>
-        <v>318957521.99066389</v>
+        <v>310105534.91522169</v>
       </c>
       <c r="Q37">
         <f>Q36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Q$35</f>
-        <v>295331038.88024431</v>
+        <v>287134754.55113119</v>
       </c>
       <c r="R37">
         <f>R36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!R$35</f>
-        <v>273454665.62985587</v>
+        <v>265865513.47326961</v>
       </c>
       <c r="S37">
         <f>S36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!S$35</f>
-        <v>253198764.47208875</v>
+        <v>246171771.7345089</v>
       </c>
       <c r="T37">
         <f>T36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!T$35</f>
-        <v>234443300.43711919</v>
+        <v>227936825.6801008</v>
       </c>
       <c r="U37">
         <f>U36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!U$35</f>
-        <v>217077130.03436959</v>
+        <v>211052616.3704637</v>
       </c>
       <c r="V37">
         <f>V36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!V$35</f>
-        <v>200997342.62441629</v>
+        <v>195419089.23191082</v>
       </c>
       <c r="W37">
         <f>W36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!W$35</f>
-        <v>186108650.57816324</v>
+        <v>180943601.14065817</v>
       </c>
       <c r="X37">
         <f>X36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!X$35</f>
-        <v>172322824.60941038</v>
+        <v>167540371.42653531</v>
       </c>
       <c r="Y37">
         <f>Y36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Y$35</f>
-        <v>159558170.93463925</v>
+        <v>155129973.54308826</v>
       </c>
       <c r="Z37">
         <f>Z36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Z$35</f>
-        <v>158620301.43581331</v>
+        <v>154520118.66585869</v>
       </c>
       <c r="AA37">
         <f>AA36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AA$35</f>
-        <v>136795414.03861386</v>
+        <v>132998948.51087812</v>
       </c>
       <c r="AB37">
         <f>AB36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AB$35</f>
-        <v>126662420.40612397</v>
+        <v>123147174.54710938</v>
       </c>
       <c r="AC37">
         <f>AC36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AC$35</f>
-        <v>117280018.89455922</v>
+        <v>114025161.61769386</v>
       </c>
       <c r="AD37">
         <f>AD36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AD$35</f>
-        <v>108592610.08755483</v>
+        <v>105578853.34971654</v>
       </c>
       <c r="AE37">
         <f>AE36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AE$35</f>
-        <v>100548713.04403225</v>
+        <v>97758197.546033829</v>
       </c>
       <c r="AF37">
         <f>AF36/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AF$35</f>
-        <v>93100660.225955769</v>
-      </c>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+        <v>90516849.579660937</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>155</v>
       </c>
@@ -22190,7 +22190,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>156</v>
       </c>
@@ -22318,7 +22318,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>157</v>
       </c>
@@ -22446,7 +22446,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>158</v>
       </c>
@@ -22574,21 +22574,21 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>159</v>
       </c>
       <c r="B43">
         <f>(SUM(B37:AF37) - SUM(B39:AF39)) / SUM(B41:AF41)</f>
-        <v>5.677808394564976</v>
-      </c>
-    </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+        <v>5.5126346444855638</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -22686,7 +22686,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>110</v>
       </c>
@@ -22696,126 +22696,126 @@
       </c>
       <c r="C47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="D47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="E47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="F47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="G47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="H47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="I47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="J47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="K47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="L47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="M47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="N47">
         <f>'Cost Components'!$Z$26* 10^6 + 'Cost Components'!$Z$7 * 10^6</f>
-        <v>980246736.84210527</v>
+        <v>954246736.84210527</v>
       </c>
       <c r="O47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="P47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="Q47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="R47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="S47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="T47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="U47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="V47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="W47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="X47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="Y47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="Z47">
         <f>'Cost Components'!$Z$26 * 10^6 + 'Cost Components'!$Z$7 * 10^6</f>
-        <v>980246736.84210527</v>
+        <v>954246736.84210527</v>
       </c>
       <c r="AA47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="AB47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="AC47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="AD47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="AE47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="AF47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
-      </c>
-    </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+        <v>885246736.84210527</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>111</v>
       </c>
@@ -22825,126 +22825,126 @@
       </c>
       <c r="C48">
         <f>C47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!C$46</f>
-        <v>843746978.55750477</v>
+        <v>819672904.48343074</v>
       </c>
       <c r="D48">
         <f>D47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!D$46</f>
-        <v>781247202.36805999</v>
+        <v>758956393.04021358</v>
       </c>
       <c r="E48">
         <f>E47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!E$46</f>
-        <v>723377039.22968519</v>
+        <v>702737400.96316075</v>
       </c>
       <c r="F48">
         <f>F47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!F$46</f>
-        <v>669793554.84230101</v>
+        <v>650682778.66959321</v>
       </c>
       <c r="G48">
         <f>G47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!G$46</f>
-        <v>620179217.44657505</v>
+        <v>602484054.32369745</v>
       </c>
       <c r="H48">
         <f>H47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!H$46</f>
-        <v>574240016.15423608</v>
+        <v>557855605.85527527</v>
       </c>
       <c r="I48">
         <f>I47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!I$46</f>
-        <v>531703718.66132963</v>
+        <v>516532968.38451415</v>
       </c>
       <c r="J48">
         <f>J47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!J$46</f>
-        <v>492318258.0197497</v>
+        <v>478271267.02269828</v>
       </c>
       <c r="K48">
         <f>K47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!K$46</f>
-        <v>455850238.9071756</v>
+        <v>442843765.76175767</v>
       </c>
       <c r="L48">
         <f>L47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!L$46</f>
-        <v>422083554.54368109</v>
+        <v>410040523.85347933</v>
       </c>
       <c r="M48">
         <f>M47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!M$46</f>
-        <v>390818106.05896395</v>
+        <v>379667151.71618456</v>
       </c>
       <c r="N48">
         <f>N47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!N$46</f>
-        <v>389269466.06783628</v>
+        <v>378944508.34304053</v>
       </c>
       <c r="O48">
         <f>O47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!O$46</f>
-        <v>335063534.00116938</v>
+        <v>325503387.95969182</v>
       </c>
       <c r="P48">
         <f>P47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!P$46</f>
-        <v>310244012.96404564</v>
+        <v>301392025.88860345</v>
       </c>
       <c r="Q48">
         <f>Q47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Q$46</f>
-        <v>287262974.9667089</v>
+        <v>279066690.63759577</v>
       </c>
       <c r="R48">
         <f>R47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!R$46</f>
-        <v>265984236.08028606</v>
+        <v>258395083.9236998</v>
       </c>
       <c r="S48">
         <f>S47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!S$46</f>
-        <v>246281700.07433891</v>
+        <v>239254707.33675906</v>
       </c>
       <c r="T48">
         <f>T47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!T$46</f>
-        <v>228038611.17994341</v>
+        <v>221532136.42292506</v>
       </c>
       <c r="U48">
         <f>U47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!U$46</f>
-        <v>211146862.20365131</v>
+        <v>205122348.53974539</v>
       </c>
       <c r="V48">
         <f>V47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!V$46</f>
-        <v>195506353.89226973</v>
+        <v>189928100.49976426</v>
       </c>
       <c r="W48">
         <f>W47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!W$46</f>
-        <v>181024401.7521016</v>
+        <v>175859352.31459653</v>
       </c>
       <c r="X48">
         <f>X47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!X$46</f>
-        <v>167615186.80750147</v>
+        <v>162832733.6246264</v>
       </c>
       <c r="Y48">
         <f>Y47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Y$46</f>
-        <v>155199247.04398283</v>
+        <v>150771049.65243185</v>
       </c>
       <c r="Z48">
         <f>Z47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Z$46</f>
-        <v>154584260.79631662</v>
+        <v>150484078.02636203</v>
       </c>
       <c r="AA48">
         <f>AA47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AA$46</f>
-        <v>133058339.37241323</v>
+        <v>129261873.84467749</v>
       </c>
       <c r="AB48">
         <f>AB47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AB$46</f>
-        <v>123202166.08556782</v>
+        <v>119686920.22655323</v>
       </c>
       <c r="AC48">
         <f>AC47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AC$46</f>
-        <v>114076079.70885909</v>
+        <v>110821222.43199374</v>
       </c>
       <c r="AD48">
         <f>AD47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AD$46</f>
-        <v>105625999.73042509</v>
+        <v>102612242.99258679</v>
       </c>
       <c r="AE48">
         <f>AE47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AE$46</f>
-        <v>97801851.602245435</v>
+        <v>95011336.104247019</v>
       </c>
       <c r="AF48">
         <f>AF47/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AF$46</f>
-        <v>90557270.002079099</v>
-      </c>
-    </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+        <v>87973459.355784267</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>155</v>
       </c>
@@ -23072,7 +23072,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>156</v>
       </c>
@@ -23200,7 +23200,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -23328,7 +23328,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>158</v>
       </c>
@@ -23456,21 +23456,21 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>159</v>
       </c>
       <c r="B54">
         <f>(SUM(B48:AF48) - SUM(B50:AF50)) / SUM(B52:AF52)</f>
-        <v>5.5152185771588691</v>
-      </c>
-    </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
+        <v>5.3500448270794587</v>
+      </c>
+    </row>
+    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>21</v>
       </c>
@@ -23568,7 +23568,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -23578,126 +23578,126 @@
       </c>
       <c r="C58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="D58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="E58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="F58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="G58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="H58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="I58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="J58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="K58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="L58">
         <f>'Cost Components'!$AF$26*10^6 + 'Cost Components'!$AF$7 * 10^6</f>
-        <v>932404631.57894742</v>
+        <v>906404631.57894742</v>
       </c>
       <c r="M58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="N58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="O58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="P58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="Q58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="R58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="S58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="T58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="U58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="V58">
         <f>'Cost Components'!$AF$26*10^6 + 'Cost Components'!$AF$7 * 10^6</f>
-        <v>932404631.57894742</v>
+        <v>906404631.57894742</v>
       </c>
       <c r="W58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="X58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="Y58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="Z58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AA58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AB58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AC58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AD58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AE58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AF58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
-      </c>
-    </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+        <v>836404631.57894742</v>
+      </c>
+    </row>
+    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -23707,126 +23707,126 @@
       </c>
       <c r="C59">
         <f>C58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!C$57</f>
-        <v>798522807.01754391</v>
+        <v>774448732.94346976</v>
       </c>
       <c r="D59">
         <f>D58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!D$57</f>
-        <v>739372969.46068871</v>
+        <v>717082160.13284242</v>
       </c>
       <c r="E59">
         <f>E58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!E$57</f>
-        <v>684604601.35248959</v>
+        <v>663964963.08596516</v>
       </c>
       <c r="F59">
         <f>F58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!F$57</f>
-        <v>633893149.40045321</v>
+        <v>614782373.22774541</v>
       </c>
       <c r="G59">
         <f>G58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!G$57</f>
-        <v>586938101.29671597</v>
+        <v>569242938.17383838</v>
       </c>
       <c r="H59">
         <f>H58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!H$57</f>
-        <v>543461204.90436661</v>
+        <v>527076794.60540581</v>
       </c>
       <c r="I59">
         <f>I58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!I$57</f>
-        <v>503204819.35589492</v>
+        <v>488034069.07907945</v>
       </c>
       <c r="J59">
         <f>J58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!J$57</f>
-        <v>465930388.29249531</v>
+        <v>451883397.29544395</v>
       </c>
       <c r="K59">
         <f>K58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!K$57</f>
-        <v>431417026.19675487</v>
+        <v>418410553.05133694</v>
       </c>
       <c r="L59">
         <f>L58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!L$57</f>
-        <v>431883753.60736758</v>
+        <v>419840722.91716582</v>
       </c>
       <c r="M59">
         <f>M58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!M$57</f>
-        <v>369870564.29762936</v>
+        <v>358719609.9548499</v>
       </c>
       <c r="N59">
         <f>N58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!N$57</f>
-        <v>342472744.72002715</v>
+        <v>332147786.99523139</v>
       </c>
       <c r="O59">
         <f>O58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!O$57</f>
-        <v>317104393.25928438</v>
+        <v>307544247.21780682</v>
       </c>
       <c r="P59">
         <f>P58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!P$57</f>
-        <v>293615178.94378179</v>
+        <v>284763191.8683396</v>
       </c>
       <c r="Q59">
         <f>Q58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Q$57</f>
-        <v>271865906.42942756</v>
+        <v>263669622.10031444</v>
       </c>
       <c r="R59">
         <f>R58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!R$57</f>
-        <v>251727691.13835886</v>
+        <v>244138538.98177263</v>
       </c>
       <c r="S59">
         <f>S58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!S$57</f>
-        <v>233081195.49848044</v>
+        <v>226054202.76090059</v>
       </c>
       <c r="T59">
         <f>T58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!T$57</f>
-        <v>215815921.75785223</v>
+        <v>209309447.00083384</v>
       </c>
       <c r="U59">
         <f>U58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!U$57</f>
-        <v>199829557.18319649</v>
+        <v>193805043.51929057</v>
       </c>
       <c r="V59">
         <f>V58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!V$57</f>
-        <v>200045742.28050295</v>
+        <v>194467488.88799748</v>
       </c>
       <c r="W59">
         <f>W58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!W$57</f>
-        <v>171321636.81686941</v>
+        <v>166156587.37936434</v>
       </c>
       <c r="X59">
         <f>X58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!X$57</f>
-        <v>158631145.20080501</v>
+        <v>153848692.01792994</v>
       </c>
       <c r="Y59">
         <f>Y58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Y$57</f>
-        <v>146880690.00074536</v>
+        <v>142452492.6091944</v>
       </c>
       <c r="Z59">
         <f>Z58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!Z$57</f>
-        <v>136000638.88957903</v>
+        <v>131900456.11962442</v>
       </c>
       <c r="AA59">
         <f>AA58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AA$57</f>
-        <v>125926517.49035095</v>
+        <v>122130051.96261519</v>
       </c>
       <c r="AB59">
         <f>AB58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AB$57</f>
-        <v>116598627.30588052</v>
+        <v>113083381.44686593</v>
       </c>
       <c r="AC59">
         <f>AC58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AC$57</f>
-        <v>107961691.94988936</v>
+        <v>104706834.673024</v>
       </c>
       <c r="AD59">
         <f>AD58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AD$57</f>
-        <v>99964529.583230883</v>
+        <v>96950772.8453926</v>
       </c>
       <c r="AE59">
         <f>AE58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AE$57</f>
-        <v>92559749.614102662</v>
+        <v>89769234.116104245</v>
       </c>
       <c r="AF59">
         <f>AF58/(1+'Study Parameters'!$C$3)^'LCOF Baseline'!AF$57</f>
-        <v>85703471.864909872</v>
-      </c>
-    </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+        <v>83119661.21861504</v>
+      </c>
+    </row>
+    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>155</v>
       </c>
@@ -23954,7 +23954,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>156</v>
       </c>
@@ -24082,7 +24082,7 @@
         <v>12124034.571075751</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>157</v>
       </c>
@@ -24210,7 +24210,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>158</v>
       </c>
@@ -24338,13 +24338,13 @@
         <v>15642985.916664211</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>159</v>
       </c>
       <c r="B65">
         <f>(SUM(B59:AF59) - SUM(B61:AF61)) / SUM(B63:AF63)</f>
-        <v>5.179064767127346</v>
+        <v>5.0138910170479321</v>
       </c>
     </row>
   </sheetData>
@@ -24355,23 +24355,23 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AF65"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -24469,7 +24469,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>110</v>
       </c>
@@ -24598,7 +24598,7 @@
         <v>1856261016.9491527</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -24727,7 +24727,7 @@
         <v>243851658.48305735</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>155</v>
       </c>
@@ -24855,7 +24855,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>156</v>
       </c>
@@ -24983,7 +24983,7 @@
         <v>16026788.292859957</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>157</v>
       </c>
@@ -25111,7 +25111,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>158</v>
       </c>
@@ -25239,7 +25239,7 @@
         <v>20678497.911303982</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -25248,12 +25248,12 @@
         <v>11.650105364161435</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -25351,7 +25351,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>110</v>
       </c>
@@ -25480,7 +25480,7 @@
         <v>1901622556.3909774</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>111</v>
       </c>
@@ -25609,7 +25609,7 @@
         <v>249810673.1492241</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>155</v>
       </c>
@@ -25737,7 +25737,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>156</v>
       </c>
@@ -25865,7 +25865,7 @@
         <v>16026788.292859957</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>157</v>
       </c>
@@ -25993,7 +25993,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>158</v>
       </c>
@@ -26121,7 +26121,7 @@
         <v>20678497.911303982</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>159</v>
       </c>
@@ -26130,12 +26130,12 @@
         <v>11.938279809506865</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -26233,7 +26233,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>110</v>
       </c>
@@ -26362,7 +26362,7 @@
         <v>1816761904.7619045</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>111</v>
       </c>
@@ -26491,7 +26491,7 @@
         <v>238662773.98485282</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>155</v>
       </c>
@@ -26619,7 +26619,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>156</v>
       </c>
@@ -26747,7 +26747,7 @@
         <v>16026788.292859957</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>157</v>
       </c>
@@ -26875,7 +26875,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>158</v>
       </c>
@@ -27003,7 +27003,7 @@
         <v>20678497.911303982</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>159</v>
       </c>
@@ -27012,12 +27012,12 @@
         <v>11.755599672709472</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -27115,7 +27115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>110</v>
       </c>
@@ -27125,126 +27125,126 @@
       </c>
       <c r="C36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="D36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="E36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="F36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="G36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="H36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="I36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="J36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="K36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="L36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="M36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="N36">
         <f>'Cost Components'!$T$26 * 10^6 + 'Cost Components'!$T$7 * 10^6</f>
-        <v>1005839999.9999999</v>
+        <v>979839999.99999988</v>
       </c>
       <c r="O36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="P36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="Q36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="R36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="S36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="T36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="U36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="V36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="W36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="X36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="Y36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="Z36">
         <f>'Cost Components'!$T$26 * 10^6 + 'Cost Components'!$T$7 * 10^6</f>
-        <v>1005839999.9999999</v>
+        <v>979839999.99999988</v>
       </c>
       <c r="AA36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="AB36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="AC36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="AD36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="AE36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
+        <v>910839999.99999988</v>
       </c>
       <c r="AF36">
         <f>'Cost Components'!$T$26 * 10^6</f>
-        <v>936839999.99999988</v>
-      </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+        <v>910839999.99999988</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -27254,126 +27254,126 @@
       </c>
       <c r="C37">
         <f>C36/(1+Inputs!$C$5)^'LCOF Baseline'!C$35</f>
-        <v>875551401.86915874</v>
+        <v>851252336.44859803</v>
       </c>
       <c r="D37">
         <f>D36/(1+Inputs!$C$5)^'LCOF Baseline'!D$35</f>
-        <v>818272338.19547546</v>
+        <v>795562931.26037192</v>
       </c>
       <c r="E37">
         <f>E36/(1+Inputs!$C$5)^'LCOF Baseline'!E$35</f>
-        <v>764740502.98642564</v>
+        <v>743516758.18726349</v>
       </c>
       <c r="F37">
         <f>F36/(1+Inputs!$C$5)^'LCOF Baseline'!F$35</f>
-        <v>714710750.45460343</v>
+        <v>694875474.94136775</v>
       </c>
       <c r="G37">
         <f>G36/(1+Inputs!$C$5)^'LCOF Baseline'!G$35</f>
-        <v>667953972.38747978</v>
+        <v>649416331.72090435</v>
       </c>
       <c r="H37">
         <f>H36/(1+Inputs!$C$5)^'LCOF Baseline'!H$35</f>
-        <v>624256048.96026146</v>
+        <v>606931151.14103222</v>
       </c>
       <c r="I37">
         <f>I36/(1+Inputs!$C$5)^'LCOF Baseline'!I$35</f>
-        <v>583416868.18716025</v>
+        <v>567225374.89816093</v>
       </c>
       <c r="J37">
         <f>J36/(1+Inputs!$C$5)^'LCOF Baseline'!J$35</f>
-        <v>545249409.52071059</v>
+        <v>530117172.80201954</v>
       </c>
       <c r="K37">
         <f>K36/(1+Inputs!$C$5)^'LCOF Baseline'!K$35</f>
-        <v>509578887.40253317</v>
+        <v>495436610.09534532</v>
       </c>
       <c r="L37">
         <f>L36/(1+Inputs!$C$5)^'LCOF Baseline'!L$35</f>
-        <v>476241950.84348893</v>
+        <v>463024869.24798632</v>
       </c>
       <c r="M37">
         <f>M36/(1+Inputs!$C$5)^'LCOF Baseline'!M$35</f>
-        <v>445085935.36774665</v>
+        <v>432733522.66166937</v>
       </c>
       <c r="N37">
         <f>N36/(1+Inputs!$C$5)^'LCOF Baseline'!N$35</f>
-        <v>446604989.08270115</v>
+        <v>435060678.14244199</v>
       </c>
       <c r="O37">
         <f>O36/(1+Inputs!$C$5)^'LCOF Baseline'!O$35</f>
-        <v>388755293.35989755</v>
+        <v>377966217.71479553</v>
       </c>
       <c r="P37">
         <f>P36/(1+Inputs!$C$5)^'LCOF Baseline'!P$35</f>
-        <v>363322704.07467061</v>
+        <v>353239455.80822015</v>
       </c>
       <c r="Q37">
         <f>Q36/(1+Inputs!$C$5)^'LCOF Baseline'!Q$35</f>
-        <v>339553929.04174817</v>
+        <v>330130332.53104687</v>
       </c>
       <c r="R37">
         <f>R36/(1+Inputs!$C$5)^'LCOF Baseline'!R$35</f>
-        <v>317340120.5997647</v>
+        <v>308533021.05705315</v>
       </c>
       <c r="S37">
         <f>S36/(1+Inputs!$C$5)^'LCOF Baseline'!S$35</f>
-        <v>296579551.96239692</v>
+        <v>288348617.81033003</v>
       </c>
       <c r="T37">
         <f>T36/(1+Inputs!$C$5)^'LCOF Baseline'!T$35</f>
-        <v>277177151.3667261</v>
+        <v>269484689.54236454</v>
       </c>
       <c r="U37">
         <f>U36/(1+Inputs!$C$5)^'LCOF Baseline'!U$35</f>
-        <v>259044066.69787484</v>
+        <v>251854850.03959301</v>
       </c>
       <c r="V37">
         <f>V36/(1+Inputs!$C$5)^'LCOF Baseline'!V$35</f>
-        <v>242097258.59614474</v>
+        <v>235378364.52298415</v>
       </c>
       <c r="W37">
         <f>W36/(1+Inputs!$C$5)^'LCOF Baseline'!W$35</f>
-        <v>226259120.1833128</v>
+        <v>219979779.92802253</v>
       </c>
       <c r="X37">
         <f>X36/(1+Inputs!$C$5)^'LCOF Baseline'!X$35</f>
-        <v>211457121.66664749</v>
+        <v>205588579.37198368</v>
       </c>
       <c r="Y37">
         <f>Y36/(1+Inputs!$C$5)^'LCOF Baseline'!Y$35</f>
-        <v>197623478.1931285</v>
+        <v>192138859.22615299</v>
       </c>
       <c r="Z37">
         <f>Z36/(1+Inputs!$C$5)^'LCOF Baseline'!Z$35</f>
-        <v>198297956.2092973</v>
+        <v>193172144.09062859</v>
       </c>
       <c r="AA37">
         <f>AA36/(1+Inputs!$C$5)^'LCOF Baseline'!AA$35</f>
-        <v>172611999.46993491</v>
+        <v>167821520.85435668</v>
       </c>
       <c r="AB37">
         <f>AB36/(1+Inputs!$C$5)^'LCOF Baseline'!AB$35</f>
-        <v>161319625.67283636</v>
+        <v>156842542.85453895</v>
       </c>
       <c r="AC37">
         <f>AC36/(1+Inputs!$C$5)^'LCOF Baseline'!AC$35</f>
-        <v>150766005.30171621</v>
+        <v>146581815.75190553</v>
       </c>
       <c r="AD37">
         <f>AD36/(1+Inputs!$C$5)^'LCOF Baseline'!AD$35</f>
-        <v>140902808.69319275</v>
+        <v>136992351.1700052</v>
       </c>
       <c r="AE37">
         <f>AE36/(1+Inputs!$C$5)^'LCOF Baseline'!AE$35</f>
-        <v>131684867.9375633</v>
+        <v>128030234.73832262</v>
       </c>
       <c r="AF37">
         <f>AF36/(1+Inputs!$C$5)^'LCOF Baseline'!AF$35</f>
-        <v>123069970.0351059</v>
-      </c>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+        <v>119654424.98908657</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>155</v>
       </c>
@@ -27501,7 +27501,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>156</v>
       </c>
@@ -27629,7 +27629,7 @@
         <v>16026788.292859957</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>157</v>
       </c>
@@ -27757,7 +27757,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>158</v>
       </c>
@@ -27885,21 +27885,21 @@
         <v>20678497.911303982</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>159</v>
       </c>
       <c r="B43">
         <f>(SUM(B37:AF37) - SUM(B39:AF39)) / SUM(B41:AF41)</f>
-        <v>5.634353476900257</v>
-      </c>
-    </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+        <v>5.4691797268208457</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -27997,7 +27997,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>110</v>
       </c>
@@ -28007,126 +28007,126 @@
       </c>
       <c r="C47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="D47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="E47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="F47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="G47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="H47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="I47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="J47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="K47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="L47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="M47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="N47">
         <f>'Cost Components'!$Z$26* 10^6 + 'Cost Components'!$Z$7 * 10^6</f>
-        <v>980246736.84210527</v>
+        <v>954246736.84210527</v>
       </c>
       <c r="O47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="P47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="Q47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="R47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="S47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="T47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="U47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="V47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="W47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="X47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="Y47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="Z47">
         <f>'Cost Components'!$Z$26 * 10^6 + 'Cost Components'!$Z$7 * 10^6</f>
-        <v>980246736.84210527</v>
+        <v>954246736.84210527</v>
       </c>
       <c r="AA47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="AB47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="AC47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="AD47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="AE47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
+        <v>885246736.84210527</v>
       </c>
       <c r="AF47">
         <f>'Cost Components'!$Z$26 * 10^6</f>
-        <v>911246736.84210527</v>
-      </c>
-    </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+        <v>885246736.84210527</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>111</v>
       </c>
@@ -28136,126 +28136,126 @@
       </c>
       <c r="C48">
         <f>C47/(1+Inputs!$C$5)^'LCOF Baseline'!C$46</f>
-        <v>851632464.3384161</v>
+        <v>827333398.91785538</v>
       </c>
       <c r="D48">
         <f>D47/(1+Inputs!$C$5)^'LCOF Baseline'!D$46</f>
-        <v>795918190.97048235</v>
+        <v>773208784.03537881</v>
       </c>
       <c r="E48">
         <f>E47/(1+Inputs!$C$5)^'LCOF Baseline'!E$46</f>
-        <v>743848776.60792744</v>
+        <v>722625031.80876529</v>
       </c>
       <c r="F48">
         <f>F47/(1+Inputs!$C$5)^'LCOF Baseline'!F$46</f>
-        <v>695185772.53077328</v>
+        <v>675350497.01753771</v>
       </c>
       <c r="G48">
         <f>G47/(1+Inputs!$C$5)^'LCOF Baseline'!G$46</f>
-        <v>649706329.46801233</v>
+        <v>631168688.80143702</v>
       </c>
       <c r="H48">
         <f>H47/(1+Inputs!$C$5)^'LCOF Baseline'!H$46</f>
-        <v>607202177.07290876</v>
+        <v>589877279.25367951</v>
       </c>
       <c r="I48">
         <f>I47/(1+Inputs!$C$5)^'LCOF Baseline'!I$46</f>
-        <v>567478670.16159701</v>
+        <v>551287176.87259758</v>
       </c>
       <c r="J48">
         <f>J47/(1+Inputs!$C$5)^'LCOF Baseline'!J$46</f>
-        <v>530353897.34728688</v>
+        <v>515221660.62859589</v>
       </c>
       <c r="K48">
         <f>K47/(1+Inputs!$C$5)^'LCOF Baseline'!K$46</f>
-        <v>495657847.98811853</v>
+        <v>481515570.68093067</v>
       </c>
       <c r="L48">
         <f>L47/(1+Inputs!$C$5)^'LCOF Baseline'!L$46</f>
-        <v>463231633.63375568</v>
+        <v>450014552.03825301</v>
       </c>
       <c r="M48">
         <f>M47/(1+Inputs!$C$5)^'LCOF Baseline'!M$46</f>
-        <v>432926760.40537906</v>
+        <v>420574347.69930184</v>
       </c>
       <c r="N48">
         <f>N47/(1+Inputs!$C$5)^'LCOF Baseline'!N$46</f>
-        <v>435241274.16460061</v>
+        <v>423696963.22434151</v>
       </c>
       <c r="O48">
         <f>O47/(1+Inputs!$C$5)^'LCOF Baseline'!O$46</f>
-        <v>378134999.04391575</v>
+        <v>367345923.39881378</v>
       </c>
       <c r="P48">
         <f>P47/(1+Inputs!$C$5)^'LCOF Baseline'!P$46</f>
-        <v>353397195.36814559</v>
+        <v>343313947.10169512</v>
       </c>
       <c r="Q48">
         <f>Q47/(1+Inputs!$C$5)^'LCOF Baseline'!Q$46</f>
-        <v>330277752.68050987</v>
+        <v>320854156.16980851</v>
       </c>
       <c r="R48">
         <f>R47/(1+Inputs!$C$5)^'LCOF Baseline'!R$46</f>
-        <v>308670796.89767277</v>
+        <v>299863697.35496122</v>
       </c>
       <c r="S48">
         <f>S47/(1+Inputs!$C$5)^'LCOF Baseline'!S$46</f>
-        <v>288477380.27819884</v>
+        <v>280246446.12613201</v>
       </c>
       <c r="T48">
         <f>T47/(1+Inputs!$C$5)^'LCOF Baseline'!T$46</f>
-        <v>269605028.29738212</v>
+        <v>261912566.47302055</v>
       </c>
       <c r="U48">
         <f>U47/(1+Inputs!$C$5)^'LCOF Baseline'!U$46</f>
-        <v>251967316.16577765</v>
+        <v>244778099.50749582</v>
       </c>
       <c r="V48">
         <f>V47/(1+Inputs!$C$5)^'LCOF Baseline'!V$46</f>
-        <v>235483473.05212867</v>
+        <v>228764578.97896808</v>
       </c>
       <c r="W48">
         <f>W47/(1+Inputs!$C$5)^'LCOF Baseline'!W$46</f>
-        <v>220078012.19825107</v>
+        <v>213798671.94296083</v>
       </c>
       <c r="X48">
         <f>X47/(1+Inputs!$C$5)^'LCOF Baseline'!X$46</f>
-        <v>205680385.23201036</v>
+        <v>199811842.93734655</v>
       </c>
       <c r="Y48">
         <f>Y47/(1+Inputs!$C$5)^'LCOF Baseline'!Y$46</f>
-        <v>192224659.09533679</v>
+        <v>186740040.12836125</v>
       </c>
       <c r="Z48">
         <f>Z47/(1+Inputs!$C$5)^'LCOF Baseline'!Z$46</f>
-        <v>193252330.88425833</v>
+        <v>188126518.76558962</v>
       </c>
       <c r="AA48">
         <f>AA47/(1+Inputs!$C$5)^'LCOF Baseline'!AA$46</f>
-        <v>167896461.78298259</v>
+        <v>163105983.16740435</v>
       </c>
       <c r="AB48">
         <f>AB47/(1+Inputs!$C$5)^'LCOF Baseline'!AB$46</f>
-        <v>156912581.10559121</v>
+        <v>152435498.28729379</v>
       </c>
       <c r="AC48">
         <f>AC47/(1+Inputs!$C$5)^'LCOF Baseline'!AC$46</f>
-        <v>146647272.06130016</v>
+        <v>142463082.51148951</v>
       </c>
       <c r="AD48">
         <f>AD47/(1+Inputs!$C$5)^'LCOF Baseline'!AD$46</f>
-        <v>137053525.29093477</v>
+        <v>133143067.76774722</v>
       </c>
       <c r="AE48">
         <f>AE47/(1+Inputs!$C$5)^'LCOF Baseline'!AE$46</f>
-        <v>128087406.81395772</v>
+        <v>124432773.61471704</v>
       </c>
       <c r="AF48">
         <f>AF47/(1+Inputs!$C$5)^'LCOF Baseline'!AF$46</f>
-        <v>119707856.83547451</v>
-      </c>
-    </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+        <v>116292311.78945518</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>155</v>
       </c>
@@ -28383,7 +28383,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>156</v>
       </c>
@@ -28511,7 +28511,7 @@
         <v>16026788.292859957</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -28639,7 +28639,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>158</v>
       </c>
@@ -28767,21 +28767,21 @@
         <v>20678497.911303982</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>159</v>
       </c>
       <c r="B54">
         <f>(SUM(B48:AF48) - SUM(B50:AF50)) / SUM(B52:AF52)</f>
-        <v>5.4717636594941528</v>
-      </c>
-    </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
+        <v>5.3065899094147477</v>
+      </c>
+    </row>
+    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>21</v>
       </c>
@@ -28879,7 +28879,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -28889,126 +28889,126 @@
       </c>
       <c r="C58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="D58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="E58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="F58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="G58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="H58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="I58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="J58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="K58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="L58">
         <f>'Cost Components'!$AF$26*10^6 + 'Cost Components'!$AF$7 * 10^6</f>
-        <v>932404631.57894742</v>
+        <v>906404631.57894742</v>
       </c>
       <c r="M58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="N58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="O58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="P58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="Q58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="R58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="S58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="T58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="U58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="V58">
         <f>'Cost Components'!$AF$26*10^6 + 'Cost Components'!$AF$7 * 10^6</f>
-        <v>932404631.57894742</v>
+        <v>906404631.57894742</v>
       </c>
       <c r="W58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="X58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="Y58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="Z58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AA58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AB58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AC58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AD58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AE58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
+        <v>836404631.57894742</v>
       </c>
       <c r="AF58">
         <f>'Cost Components'!$AF$26*10^6</f>
-        <v>862404631.57894742</v>
-      </c>
-    </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+        <v>836404631.57894742</v>
+      </c>
+    </row>
+    <row r="59" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -29018,126 +29018,126 @@
       </c>
       <c r="C59">
         <f>C58/(1+Inputs!$C$5)^'LCOF Baseline'!C$57</f>
-        <v>805985636.9896704</v>
+        <v>781686571.56910968</v>
       </c>
       <c r="D59">
         <f>D58/(1+Inputs!$C$5)^'LCOF Baseline'!D$57</f>
-        <v>753257604.66324341</v>
+        <v>730548197.72813988</v>
       </c>
       <c r="E59">
         <f>E58/(1+Inputs!$C$5)^'LCOF Baseline'!E$57</f>
-        <v>703979069.77873218</v>
+        <v>682755324.97957003</v>
       </c>
       <c r="F59">
         <f>F58/(1+Inputs!$C$5)^'LCOF Baseline'!F$57</f>
-        <v>657924364.27918899</v>
+        <v>638089088.7659533</v>
       </c>
       <c r="G59">
         <f>G58/(1+Inputs!$C$5)^'LCOF Baseline'!G$57</f>
-        <v>614882583.43849432</v>
+        <v>596344942.77191889</v>
       </c>
       <c r="H59">
         <f>H58/(1+Inputs!$C$5)^'LCOF Baseline'!H$57</f>
-        <v>574656620.03597605</v>
+        <v>557331722.21674669</v>
       </c>
       <c r="I59">
         <f>I58/(1+Inputs!$C$5)^'LCOF Baseline'!I$57</f>
-        <v>537062261.71586537</v>
+        <v>520870768.42686605</v>
       </c>
       <c r="J59">
         <f>J58/(1+Inputs!$C$5)^'LCOF Baseline'!J$57</f>
-        <v>501927347.39800507</v>
+        <v>486795110.67931408</v>
       </c>
       <c r="K59">
         <f>K58/(1+Inputs!$C$5)^'LCOF Baseline'!K$57</f>
-        <v>469090978.8766402</v>
+        <v>454948701.56945235</v>
       </c>
       <c r="L59">
         <f>L58/(1+Inputs!$C$5)^'LCOF Baseline'!L$57</f>
-        <v>473987234.44629025</v>
+        <v>460770152.85078758</v>
       </c>
       <c r="M59">
         <f>M58/(1+Inputs!$C$5)^'LCOF Baseline'!M$57</f>
-        <v>409722228.03444856</v>
+        <v>397369815.32837129</v>
       </c>
       <c r="N59">
         <f>N58/(1+Inputs!$C$5)^'LCOF Baseline'!N$57</f>
-        <v>382917970.12565291</v>
+        <v>371373659.18539381</v>
       </c>
       <c r="O59">
         <f>O58/(1+Inputs!$C$5)^'LCOF Baseline'!O$57</f>
-        <v>357867261.79967558</v>
+        <v>347078186.15457362</v>
       </c>
       <c r="P59">
         <f>P58/(1+Inputs!$C$5)^'LCOF Baseline'!P$57</f>
-        <v>334455384.85950994</v>
+        <v>324372136.59305948</v>
       </c>
       <c r="Q59">
         <f>Q58/(1+Inputs!$C$5)^'LCOF Baseline'!Q$57</f>
-        <v>312575126.03692514</v>
+        <v>303151529.52622378</v>
       </c>
       <c r="R59">
         <f>R58/(1+Inputs!$C$5)^'LCOF Baseline'!R$57</f>
-        <v>292126286.01581794</v>
+        <v>283319186.47310638</v>
       </c>
       <c r="S59">
         <f>S58/(1+Inputs!$C$5)^'LCOF Baseline'!S$57</f>
-        <v>273015220.57553077</v>
+        <v>264784286.42346391</v>
       </c>
       <c r="T59">
         <f>T58/(1+Inputs!$C$5)^'LCOF Baseline'!T$57</f>
-        <v>255154411.75283247</v>
+        <v>247461949.92847094</v>
       </c>
       <c r="U59">
         <f>U58/(1+Inputs!$C$5)^'LCOF Baseline'!U$57</f>
-        <v>238462067.05872193</v>
+        <v>231272850.4004401</v>
       </c>
       <c r="V59">
         <f>V58/(1+Inputs!$C$5)^'LCOF Baseline'!V$57</f>
-        <v>240951075.11166424</v>
+        <v>234232181.03850365</v>
       </c>
       <c r="W59">
         <f>W58/(1+Inputs!$C$5)^'LCOF Baseline'!W$57</f>
-        <v>208282004.59317139</v>
+        <v>202002664.33788115</v>
       </c>
       <c r="X59">
         <f>X58/(1+Inputs!$C$5)^'LCOF Baseline'!X$57</f>
-        <v>194656079.0590387</v>
+        <v>188787536.76437488</v>
       </c>
       <c r="Y59">
         <f>Y58/(1+Inputs!$C$5)^'LCOF Baseline'!Y$57</f>
-        <v>181921569.21405485</v>
+        <v>176436950.24707934</v>
       </c>
       <c r="Z59">
         <f>Z58/(1+Inputs!$C$5)^'LCOF Baseline'!Z$57</f>
-        <v>170020158.14397648</v>
+        <v>164894346.02530777</v>
       </c>
       <c r="AA59">
         <f>AA58/(1+Inputs!$C$5)^'LCOF Baseline'!AA$57</f>
-        <v>158897344.05979109</v>
+        <v>154106865.44421288</v>
       </c>
       <c r="AB59">
         <f>AB58/(1+Inputs!$C$5)^'LCOF Baseline'!AB$57</f>
-        <v>148502190.71008515</v>
+        <v>144025107.89178774</v>
       </c>
       <c r="AC59">
         <f>AC58/(1+Inputs!$C$5)^'LCOF Baseline'!AC$57</f>
-        <v>138787094.12157488</v>
+        <v>134602904.57176423</v>
       </c>
       <c r="AD59">
         <f>AD58/(1+Inputs!$C$5)^'LCOF Baseline'!AD$57</f>
-        <v>129707564.59960271</v>
+        <v>125797107.07641518</v>
       </c>
       <c r="AE59">
         <f>AE58/(1+Inputs!$C$5)^'LCOF Baseline'!AE$57</f>
-        <v>121222022.99028291</v>
+        <v>117567389.79104222</v>
       </c>
       <c r="AF59">
         <f>AF58/(1+Inputs!$C$5)^'LCOF Baseline'!AF$57</f>
-        <v>113291610.27129245</v>
-      </c>
-    </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+        <v>109876065.22527312</v>
+      </c>
+    </row>
+    <row r="60" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>155</v>
       </c>
@@ -29265,7 +29265,7 @@
         <v>122000000</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>156</v>
       </c>
@@ -29393,7 +29393,7 @@
         <v>16026788.292859957</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>157</v>
       </c>
@@ -29521,7 +29521,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>158</v>
       </c>
@@ -29649,13 +29649,13 @@
         <v>20678497.911303982</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>159</v>
       </c>
       <c r="B65">
         <f>(SUM(B59:AF59) - SUM(B61:AF61)) / SUM(B63:AF63)</f>
-        <v>5.1381500496500747</v>
+        <v>4.9729762995706661</v>
       </c>
     </row>
   </sheetData>
